--- a/compare_results_roots.xlsx
+++ b/compare_results_roots.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ville\OneDrive\Documents\CIC\Tesis\Experimentos finales\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ville\OneDrive\Documents\CIC\Tesis\graficas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5A9407-5F06-473F-BDC6-CBFE5F8B0450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DFEBE5-F13E-441C-A7CF-AFBC98D6F7F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{D000E91A-FD86-43AE-BED0-C7262648B88B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D000E91A-FD86-43AE-BED0-C7262648B88B}"/>
   </bookViews>
   <sheets>
     <sheet name="compare_results_1_roots" sheetId="1" r:id="rId1"/>
@@ -1401,14 +1401,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="13" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1457,9 +1456,6 @@
   <dxfs count="23">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1542,6 +1538,9 @@
       <numFmt numFmtId="164" formatCode="0.000"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
@@ -1599,7 +1598,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{22486A75-2371-4853-9228-56B68DF7A72B}" name="Table1" displayName="Table1" ref="A1:AH51">
   <autoFilter ref="A1:AH51" xr:uid="{22486A75-2371-4853-9228-56B68DF7A72B}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AH51">
-    <sortCondition ref="T1:T51"/>
+    <sortCondition ref="A1:A51"/>
   </sortState>
   <tableColumns count="34">
     <tableColumn id="1" xr3:uid="{71466FF1-D561-4754-A735-826C30565FE1}" name="experiment" totalsRowLabel="Total"/>
@@ -1670,7 +1669,7 @@
     <tableColumn id="9" xr3:uid="{966E8F23-6EDA-4765-8CF7-44BFD50307ED}" name="GAP Rollout k=3" dataDxfId="12">
       <calculatedColumnFormula>((Table2[[#This Row],[Prom. Nodos salvados óptimo IQCP]]-Table2[[#This Row],[Prom. Nodos salvados Rollout k=3]])/Table2[[#This Row],[Prom. Nodos salvados óptimo IQCP]])*100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{3DE6C6BE-9A02-4802-8EFE-FD70CA824AA2}" name="Greedy" dataDxfId="1">
+    <tableColumn id="10" xr3:uid="{3DE6C6BE-9A02-4802-8EFE-FD70CA824AA2}" name="Greedy" dataDxfId="11">
       <calculatedColumnFormula>AVERAGEIF(Table1[root degree],Table2[[#This Row],[Grado raíz]],Table1[optimal_greedy])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1679,29 +1678,29 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5BCCF9EA-4194-4328-B98B-770C12B8282F}" name="Table3" displayName="Table3" ref="A12:I17" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5BCCF9EA-4194-4328-B98B-770C12B8282F}" name="Table3" displayName="Table3" ref="A12:I17" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8">
   <autoFilter ref="A12:I17" xr:uid="{5BCCF9EA-4194-4328-B98B-770C12B8282F}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{76F1B0EC-277A-4EA8-A355-38D872CA19BD}" name="Grado raíz"/>
-    <tableColumn id="2" xr3:uid="{12C8B7F5-D8E1-4575-BB15-E3D30EFADC19}" name="Instancias" dataDxfId="8">
+    <tableColumn id="2" xr3:uid="{12C8B7F5-D8E1-4575-BB15-E3D30EFADC19}" name="Instancias" dataDxfId="7">
       <calculatedColumnFormula>COUNTIF(Table1[root degree],Table3[[#This Row],[Grado raíz]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{807F8B9C-9C73-4E16-B969-B6D1C49529D8}" name="Prom. T-CPU MIQCP" dataDxfId="7">
+    <tableColumn id="3" xr3:uid="{807F8B9C-9C73-4E16-B969-B6D1C49529D8}" name="Prom. T-CPU MIQCP" dataDxfId="6">
       <calculatedColumnFormula>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[duration_miqcp])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{9B6B7C7D-4350-449F-9EE6-176B59DADAEE}" name="Prom. T-CPU IQCP" dataDxfId="6">
+    <tableColumn id="4" xr3:uid="{9B6B7C7D-4350-449F-9EE6-176B59DADAEE}" name="Prom. T-CPU IQCP" dataDxfId="5">
       <calculatedColumnFormula>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[duration_iqcp])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{0C3B864F-0EDF-49C5-A55E-2323AD38DAB7}" name="Prom. T-CPU ILP" dataDxfId="5">
+    <tableColumn id="5" xr3:uid="{0C3B864F-0EDF-49C5-A55E-2323AD38DAB7}" name="Prom. T-CPU ILP" dataDxfId="4">
       <calculatedColumnFormula>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[duration_ilp])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{907521A4-48A5-47D0-A89B-57B18E7B64EF}" name="Prom. T-CPU Rollout k=1" dataDxfId="4">
+    <tableColumn id="6" xr3:uid="{907521A4-48A5-47D0-A89B-57B18E7B64EF}" name="Prom. T-CPU Rollout k=1" dataDxfId="3">
       <calculatedColumnFormula>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[time_taken k=1])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{E86CF385-0633-460D-BFCE-9BA31C8325D2}" name="Prom. T-CPU Rollout k=2" dataDxfId="3">
+    <tableColumn id="7" xr3:uid="{E86CF385-0633-460D-BFCE-9BA31C8325D2}" name="Prom. T-CPU Rollout k=2" dataDxfId="2">
       <calculatedColumnFormula>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[time_taken k=2])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{06012AAB-F151-4FD2-B0BC-09B17B2BDBCC}" name="Prom. T-CPU Rollout k=3" dataDxfId="2">
+    <tableColumn id="8" xr3:uid="{06012AAB-F151-4FD2-B0BC-09B17B2BDBCC}" name="Prom. T-CPU Rollout k=3" dataDxfId="1">
       <calculatedColumnFormula>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[time_taken k=3])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{1BBE5458-6827-4BF0-B481-BBB72DAE5882}" name="Greedy" dataDxfId="0">
@@ -2082,44 +2081,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542405D3-32E2-4D19-8EBF-16429DDA6C9C}">
   <dimension ref="A1:AH51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="13.5703125" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" customWidth="1"/>
+    <col min="1" max="2" width="13.54296875" customWidth="1"/>
+    <col min="3" max="3" width="10.7265625" customWidth="1"/>
+    <col min="4" max="4" width="13.81640625" customWidth="1"/>
+    <col min="5" max="5" width="13.7265625" customWidth="1"/>
+    <col min="6" max="6" width="13.1796875" customWidth="1"/>
+    <col min="7" max="7" width="15.453125" customWidth="1"/>
+    <col min="8" max="8" width="15.26953125" customWidth="1"/>
+    <col min="9" max="9" width="14.7265625" customWidth="1"/>
     <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.140625" customWidth="1"/>
+    <col min="11" max="11" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.1796875" customWidth="1"/>
     <col min="14" max="14" width="17" customWidth="1"/>
-    <col min="15" max="15" width="16.42578125" customWidth="1"/>
-    <col min="16" max="16" width="17.7109375" customWidth="1"/>
-    <col min="17" max="17" width="17.5703125" customWidth="1"/>
+    <col min="15" max="15" width="16.453125" customWidth="1"/>
+    <col min="16" max="16" width="17.7265625" customWidth="1"/>
+    <col min="17" max="17" width="17.54296875" customWidth="1"/>
     <col min="18" max="18" width="17" customWidth="1"/>
-    <col min="19" max="19" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.5703125" customWidth="1"/>
-    <col min="21" max="21" width="20.28515625" customWidth="1"/>
-    <col min="22" max="22" width="21.28515625" customWidth="1"/>
-    <col min="23" max="23" width="23.5703125" customWidth="1"/>
-    <col min="24" max="24" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="16.5703125" customWidth="1"/>
-    <col min="26" max="26" width="20.28515625" customWidth="1"/>
-    <col min="27" max="27" width="21.28515625" customWidth="1"/>
-    <col min="28" max="28" width="23.5703125" customWidth="1"/>
-    <col min="29" max="29" width="20.85546875" customWidth="1"/>
-    <col min="30" max="30" width="16.5703125" customWidth="1"/>
-    <col min="31" max="31" width="20.28515625" customWidth="1"/>
-    <col min="32" max="32" width="21.28515625" customWidth="1"/>
-    <col min="33" max="33" width="19.7109375" customWidth="1"/>
-    <col min="34" max="34" width="23.5703125" customWidth="1"/>
+    <col min="19" max="19" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.54296875" customWidth="1"/>
+    <col min="21" max="21" width="20.26953125" customWidth="1"/>
+    <col min="22" max="22" width="21.26953125" customWidth="1"/>
+    <col min="23" max="23" width="23.54296875" customWidth="1"/>
+    <col min="24" max="24" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.54296875" customWidth="1"/>
+    <col min="26" max="26" width="20.26953125" customWidth="1"/>
+    <col min="27" max="27" width="21.26953125" customWidth="1"/>
+    <col min="28" max="28" width="23.54296875" customWidth="1"/>
+    <col min="29" max="29" width="20.81640625" customWidth="1"/>
+    <col min="30" max="30" width="16.54296875" customWidth="1"/>
+    <col min="31" max="31" width="20.26953125" customWidth="1"/>
+    <col min="32" max="32" width="21.26953125" customWidth="1"/>
+    <col min="33" max="33" width="19.7265625" customWidth="1"/>
+    <col min="34" max="34" width="23.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2223,69 +2222,63 @@
         <v>258</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>40</v>
       </c>
       <c r="D2">
-        <v>2010.4343097209901</v>
+        <v>41355.2283542156</v>
       </c>
       <c r="E2" t="s">
-        <v>107</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>65.932975530624304</v>
+        <v>60.771632432937601</v>
       </c>
       <c r="H2" t="s">
-        <v>107</v>
+        <v>14</v>
       </c>
       <c r="I2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J2">
-        <v>297.85724782943697</v>
+        <v>270.91339325904801</v>
       </c>
       <c r="K2" t="s">
-        <v>107</v>
+        <v>14</v>
       </c>
       <c r="L2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M2">
-        <v>34203.160275936098</v>
-      </c>
-      <c r="N2" t="s">
-        <v>107</v>
-      </c>
-      <c r="O2">
-        <v>34</v>
+        <v>86400.129969119997</v>
       </c>
       <c r="P2">
-        <v>4.5621395111083898E-3</v>
+        <v>5.8391094207763602E-3</v>
       </c>
       <c r="Q2" t="s">
-        <v>107</v>
+        <v>14</v>
       </c>
       <c r="R2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S2" t="s">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="T2">
-        <v>7.3529333999886107E-2</v>
+        <v>8.6160457999994805E-2</v>
       </c>
       <c r="U2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V2">
         <v>0</v>
@@ -2294,13 +2287,13 @@
         <v>0</v>
       </c>
       <c r="X2" t="s">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="Y2">
-        <v>0.52385645800040903</v>
+        <v>0.77138975100024199</v>
       </c>
       <c r="Z2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA2">
         <v>0</v>
@@ -2309,13 +2302,13 @@
         <v>0</v>
       </c>
       <c r="AC2" t="s">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="AD2">
-        <v>1.1891566680005701</v>
+        <v>2.9789236259994101</v>
       </c>
       <c r="AE2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF2">
         <v>0</v>
@@ -2327,93 +2320,93 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C3">
         <v>40</v>
       </c>
       <c r="D3">
-        <v>28681.8346641063</v>
+        <v>43866.964335918397</v>
       </c>
       <c r="E3" t="s">
-        <v>191</v>
+        <v>16</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>638.05624175071705</v>
+        <v>57.756932735443101</v>
       </c>
       <c r="H3" t="s">
-        <v>192</v>
+        <v>16</v>
       </c>
       <c r="I3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J3">
-        <v>463.24853658676102</v>
+        <v>187.91967535018901</v>
       </c>
       <c r="K3" t="s">
-        <v>193</v>
+        <v>16</v>
       </c>
       <c r="L3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="M3">
-        <v>86400.312841892199</v>
+        <v>86400.254833221406</v>
       </c>
       <c r="P3">
-        <v>5.4316520690917899E-3</v>
+        <v>4.7655105590820304E-3</v>
       </c>
       <c r="Q3" t="s">
-        <v>194</v>
+        <v>16</v>
       </c>
       <c r="R3">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="S3" t="s">
-        <v>195</v>
+        <v>17</v>
       </c>
       <c r="T3">
-        <v>7.6273958000001502E-2</v>
+        <v>8.6154125000120901E-2</v>
       </c>
       <c r="U3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="V3">
         <v>0</v>
       </c>
       <c r="W3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="Y3">
-        <v>0.83446166699923197</v>
+        <v>1.08466354199936</v>
       </c>
       <c r="Z3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="AD3">
-        <v>3.0783139179993602</v>
+        <v>3.1687015020006499</v>
       </c>
       <c r="AE3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AF3">
         <v>0</v>
@@ -2422,93 +2415,93 @@
         <v>0</v>
       </c>
       <c r="AH3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4">
         <v>40</v>
       </c>
       <c r="D4">
-        <v>3774.74291229248</v>
+        <v>453.44278931617703</v>
       </c>
       <c r="E4" t="s">
-        <v>138</v>
+        <v>18</v>
       </c>
       <c r="F4">
         <v>33</v>
       </c>
       <c r="G4">
-        <v>100.92551684379499</v>
+        <v>47.695116281509399</v>
       </c>
       <c r="H4" t="s">
-        <v>138</v>
+        <v>19</v>
       </c>
       <c r="I4">
         <v>33</v>
       </c>
       <c r="J4">
-        <v>302.64456987380902</v>
+        <v>196.83315134048399</v>
       </c>
       <c r="K4" t="s">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="L4">
         <v>33</v>
       </c>
       <c r="M4">
-        <v>86400.140103101701</v>
+        <v>86400.139185190201</v>
       </c>
       <c r="P4">
-        <v>5.6214332580566398E-3</v>
+        <v>5.6414604187011701E-3</v>
       </c>
       <c r="Q4" t="s">
-        <v>140</v>
+        <v>21</v>
       </c>
       <c r="R4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S4" t="s">
-        <v>141</v>
+        <v>22</v>
       </c>
       <c r="T4">
-        <v>8.1198459000006495E-2</v>
+        <v>0.14114279199975499</v>
       </c>
       <c r="U4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X4" t="s">
-        <v>226</v>
+        <v>22</v>
       </c>
       <c r="Y4">
-        <v>0.54410941700007198</v>
+        <v>0.39363883399983002</v>
       </c>
       <c r="Z4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AA4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="AD4">
-        <v>3.3834880430003902</v>
+        <v>2.1978573339993002</v>
       </c>
       <c r="AE4">
         <v>33</v>
@@ -2520,96 +2513,96 @@
         <v>0</v>
       </c>
       <c r="AH4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="B5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C5">
         <v>40</v>
       </c>
       <c r="D5">
-        <v>1964.59009075164</v>
+        <v>396.46075916290198</v>
       </c>
       <c r="E5" t="s">
-        <v>142</v>
+        <v>23</v>
       </c>
       <c r="F5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G5">
-        <v>136.314377784729</v>
+        <v>51.4951264858245</v>
       </c>
       <c r="H5" t="s">
-        <v>143</v>
+        <v>24</v>
       </c>
       <c r="I5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J5">
-        <v>394.49784350395203</v>
+        <v>215.09952902793799</v>
       </c>
       <c r="K5" t="s">
-        <v>143</v>
+        <v>24</v>
       </c>
       <c r="L5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M5">
-        <v>86400.115904331207</v>
+        <v>86400.1290633678</v>
       </c>
       <c r="P5">
-        <v>5.6524276733398403E-3</v>
+        <v>5.5739879608154297E-3</v>
       </c>
       <c r="Q5" t="s">
-        <v>144</v>
+        <v>25</v>
       </c>
       <c r="R5">
         <v>33</v>
       </c>
       <c r="S5" t="s">
-        <v>145</v>
+        <v>26</v>
       </c>
       <c r="T5">
-        <v>8.3501915999931897E-2</v>
+        <v>0.19206783400022601</v>
       </c>
       <c r="U5">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="W5">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="X5" t="s">
-        <v>145</v>
+        <v>213</v>
       </c>
       <c r="Y5">
-        <v>0.84210574999997301</v>
+        <v>0.43922858400037501</v>
       </c>
       <c r="Z5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC5" t="s">
-        <v>145</v>
+        <v>239</v>
       </c>
       <c r="AD5">
-        <v>1.81597325100028</v>
+        <v>1.8165461259995901</v>
       </c>
       <c r="AE5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF5">
         <v>0</v>
@@ -2618,12 +2611,12 @@
         <v>0</v>
       </c>
       <c r="AH5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B6">
         <v>3</v>
@@ -2632,52 +2625,52 @@
         <v>40</v>
       </c>
       <c r="D6">
-        <v>43866.964335918397</v>
+        <v>4296.8034508228302</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G6">
-        <v>57.756932735443101</v>
+        <v>44.4875199794769</v>
       </c>
       <c r="H6" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="I6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J6">
-        <v>187.91967535018901</v>
+        <v>188.74511742591801</v>
       </c>
       <c r="K6" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="L6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="M6">
-        <v>86400.254833221406</v>
+        <v>86400.489632844896</v>
       </c>
       <c r="P6">
-        <v>4.7655105590820304E-3</v>
+        <v>5.0759315490722604E-3</v>
       </c>
       <c r="Q6" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="R6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="S6" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="T6">
-        <v>8.6154125000120901E-2</v>
+        <v>0.110329999999976</v>
       </c>
       <c r="U6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="V6">
         <v>0</v>
@@ -2686,13 +2679,13 @@
         <v>0</v>
       </c>
       <c r="X6" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="Y6">
-        <v>1.08466354199936</v>
+        <v>0.43649625000034498</v>
       </c>
       <c r="Z6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA6">
         <v>0</v>
@@ -2701,13 +2694,13 @@
         <v>0</v>
       </c>
       <c r="AC6" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="AD6">
-        <v>3.1687015020006499</v>
+        <v>1.4178213759996601</v>
       </c>
       <c r="AE6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF6">
         <v>0</v>
@@ -2719,9 +2712,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -2730,49 +2723,49 @@
         <v>40</v>
       </c>
       <c r="D7">
-        <v>41355.2283542156</v>
+        <v>2946.5776097774501</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F7">
         <v>36</v>
       </c>
       <c r="G7">
-        <v>60.771632432937601</v>
+        <v>45.887658596038797</v>
       </c>
       <c r="H7" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="I7">
         <v>36</v>
       </c>
       <c r="J7">
-        <v>270.91339325904801</v>
+        <v>111.08167362213101</v>
       </c>
       <c r="K7" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="L7">
         <v>36</v>
       </c>
       <c r="M7">
-        <v>86400.129969119997</v>
+        <v>86400.133324861497</v>
       </c>
       <c r="P7">
-        <v>5.8391094207763602E-3</v>
+        <v>4.7135353088378898E-3</v>
       </c>
       <c r="Q7" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="R7">
         <v>36</v>
       </c>
       <c r="S7" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="T7">
-        <v>8.6160457999994805E-2</v>
+        <v>0.22504466700001999</v>
       </c>
       <c r="U7">
         <v>36</v>
@@ -2784,10 +2777,10 @@
         <v>0</v>
       </c>
       <c r="X7" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="Y7">
-        <v>0.77138975100024199</v>
+        <v>1.8452987929995199</v>
       </c>
       <c r="Z7">
         <v>36</v>
@@ -2799,10 +2792,10 @@
         <v>0</v>
       </c>
       <c r="AC7" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="AD7">
-        <v>2.9789236259994101</v>
+        <v>5.5470325030000804</v>
       </c>
       <c r="AE7">
         <v>36</v>
@@ -2817,93 +2810,93 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C8">
         <v>40</v>
       </c>
       <c r="D8">
-        <v>18.745156764984099</v>
+        <v>1297.5956439971901</v>
       </c>
       <c r="E8" t="s">
-        <v>205</v>
+        <v>32</v>
       </c>
       <c r="F8">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G8">
-        <v>163.14162302017201</v>
+        <v>77.707883358001695</v>
       </c>
       <c r="H8" t="s">
-        <v>205</v>
+        <v>33</v>
       </c>
       <c r="I8">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J8">
-        <v>452.50598287582397</v>
+        <v>256.97025418281498</v>
       </c>
       <c r="K8" t="s">
-        <v>205</v>
+        <v>33</v>
       </c>
       <c r="L8">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M8">
-        <v>86400.124464988694</v>
+        <v>86400.128589868502</v>
       </c>
       <c r="P8">
-        <v>4.9333572387695304E-3</v>
+        <v>5.3551197052001901E-3</v>
       </c>
       <c r="Q8" t="s">
-        <v>206</v>
+        <v>34</v>
       </c>
       <c r="R8">
         <v>29</v>
       </c>
       <c r="S8" t="s">
-        <v>207</v>
+        <v>35</v>
       </c>
       <c r="T8">
-        <v>9.0025083000000394E-2</v>
+        <v>0.157853499999873</v>
       </c>
       <c r="U8">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V8">
         <v>0</v>
       </c>
       <c r="W8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="X8" t="s">
-        <v>207</v>
+        <v>35</v>
       </c>
       <c r="Y8">
-        <v>0.32029962500018799</v>
+        <v>0.87887870899976395</v>
       </c>
       <c r="Z8">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC8" t="s">
-        <v>207</v>
+        <v>35</v>
       </c>
       <c r="AD8">
-        <v>0.65302429199982703</v>
+        <v>2.4873180009999398</v>
       </c>
       <c r="AE8">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="AF8">
         <v>0</v>
@@ -2912,96 +2905,96 @@
         <v>0</v>
       </c>
       <c r="AH8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C9">
         <v>40</v>
       </c>
       <c r="D9">
-        <v>340.20367479324301</v>
+        <v>362.63930082321099</v>
       </c>
       <c r="E9" t="s">
-        <v>150</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G9">
-        <v>59.518777132034302</v>
+        <v>78.8139390945434</v>
       </c>
       <c r="H9" t="s">
-        <v>150</v>
+        <v>36</v>
       </c>
       <c r="I9">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J9">
-        <v>248.66281890869101</v>
+        <v>297.10240054130497</v>
       </c>
       <c r="K9" t="s">
-        <v>151</v>
+        <v>36</v>
       </c>
       <c r="L9">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M9">
-        <v>86400.133429527195</v>
+        <v>86400.132736921296</v>
       </c>
       <c r="P9">
-        <v>4.7066211700439401E-3</v>
+        <v>4.8964023590087804E-3</v>
       </c>
       <c r="Q9" t="s">
-        <v>151</v>
+        <v>37</v>
       </c>
       <c r="R9">
         <v>31</v>
       </c>
       <c r="S9" t="s">
-        <v>152</v>
+        <v>38</v>
       </c>
       <c r="T9">
-        <v>9.1725875000065502E-2</v>
+        <v>0.16448504199979599</v>
       </c>
       <c r="U9">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V9">
         <v>0</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X9" t="s">
-        <v>152</v>
+        <v>38</v>
       </c>
       <c r="Y9">
-        <v>0.126252750000276</v>
+        <v>0.51000645900057795</v>
       </c>
       <c r="Z9">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="s">
-        <v>152</v>
+        <v>240</v>
       </c>
       <c r="AD9">
-        <v>0.91174570899966001</v>
+        <v>1.67395616799967</v>
       </c>
       <c r="AE9">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="AF9">
         <v>0</v>
@@ -3010,96 +3003,96 @@
         <v>0</v>
       </c>
       <c r="AH9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10">
         <v>40</v>
       </c>
       <c r="D10">
-        <v>759.06535601615894</v>
+        <v>471.46557950973499</v>
       </c>
       <c r="E10" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="F10">
+        <v>33</v>
+      </c>
+      <c r="G10">
+        <v>77.797639846801701</v>
+      </c>
+      <c r="H10" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10">
+        <v>33</v>
+      </c>
+      <c r="J10">
+        <v>244.49754166603</v>
+      </c>
+      <c r="K10" t="s">
+        <v>39</v>
+      </c>
+      <c r="L10">
+        <v>33</v>
+      </c>
+      <c r="M10">
+        <v>86400.1265144348</v>
+      </c>
+      <c r="P10">
+        <v>4.8739910125732396E-3</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>41</v>
+      </c>
+      <c r="R10">
         <v>29</v>
       </c>
-      <c r="G10">
-        <v>912.31764340400696</v>
-      </c>
-      <c r="H10" t="s">
-        <v>84</v>
-      </c>
-      <c r="I10">
-        <v>29</v>
-      </c>
-      <c r="J10">
-        <v>540.48723745346001</v>
-      </c>
-      <c r="K10" t="s">
-        <v>85</v>
-      </c>
-      <c r="L10">
-        <v>29</v>
-      </c>
-      <c r="M10">
-        <v>86400.132619380907</v>
-      </c>
-      <c r="P10">
-        <v>4.8832893371581997E-3</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>86</v>
-      </c>
-      <c r="R10">
-        <v>28</v>
-      </c>
       <c r="S10" t="s">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="T10">
-        <v>0.10059033400011599</v>
+        <v>0.184896415999901</v>
       </c>
       <c r="U10">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="V10">
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X10" t="s">
-        <v>87</v>
+        <v>214</v>
       </c>
       <c r="Y10">
-        <v>0.36835916700056198</v>
+        <v>0.99781641700064905</v>
       </c>
       <c r="Z10">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AA10">
         <v>-1</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC10" t="s">
-        <v>87</v>
+        <v>214</v>
       </c>
       <c r="AD10">
-        <v>0.92678079200049901</v>
+        <v>3.3030031670004898</v>
       </c>
       <c r="AE10">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AF10">
         <v>-1</v>
@@ -3108,63 +3101,63 @@
         <v>-1</v>
       </c>
       <c r="AH10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11">
         <v>40</v>
       </c>
       <c r="D11">
-        <v>1160.6931722164099</v>
+        <v>434.91103124618502</v>
       </c>
       <c r="E11" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="F11">
         <v>36</v>
       </c>
       <c r="G11">
-        <v>60.158497571945098</v>
+        <v>51.784494161605799</v>
       </c>
       <c r="H11" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="I11">
         <v>36</v>
       </c>
       <c r="J11">
-        <v>220.47335624694799</v>
+        <v>268.26836252212502</v>
       </c>
       <c r="K11" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="L11">
         <v>36</v>
       </c>
       <c r="M11">
-        <v>86400.164609908999</v>
+        <v>86400.137657165498</v>
       </c>
       <c r="P11">
-        <v>5.1751136779785104E-3</v>
+        <v>5.3925514221191398E-3</v>
       </c>
       <c r="Q11" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="R11">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="S11" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="T11">
-        <v>0.101051209000161</v>
+        <v>0.129812333000245</v>
       </c>
       <c r="U11">
         <v>36</v>
@@ -3173,13 +3166,13 @@
         <v>0</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" t="s">
-        <v>69</v>
+        <v>215</v>
       </c>
       <c r="Y11">
-        <v>0.438611583000238</v>
+        <v>1.0161245420003899</v>
       </c>
       <c r="Z11">
         <v>36</v>
@@ -3188,13 +3181,13 @@
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC11" t="s">
-        <v>69</v>
+        <v>215</v>
       </c>
       <c r="AD11">
-        <v>1.18862187499962</v>
+        <v>2.1120852509993702</v>
       </c>
       <c r="AE11">
         <v>36</v>
@@ -3206,93 +3199,93 @@
         <v>0</v>
       </c>
       <c r="AH11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="B12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C12">
         <v>40</v>
       </c>
       <c r="D12">
-        <v>922.62835550308205</v>
+        <v>236.19271969795199</v>
       </c>
       <c r="E12" t="s">
-        <v>165</v>
+        <v>47</v>
       </c>
       <c r="F12">
         <v>33</v>
       </c>
       <c r="G12">
-        <v>280.592938423156</v>
+        <v>51.336097240447998</v>
       </c>
       <c r="H12" t="s">
-        <v>165</v>
+        <v>48</v>
       </c>
       <c r="I12">
         <v>33</v>
       </c>
       <c r="J12">
-        <v>412.89148020744301</v>
+        <v>230.964210748672</v>
       </c>
       <c r="K12" t="s">
-        <v>165</v>
+        <v>47</v>
       </c>
       <c r="L12">
         <v>33</v>
       </c>
       <c r="M12">
-        <v>86400.128802537904</v>
+        <v>86400.596881627993</v>
       </c>
       <c r="P12">
-        <v>5.1181316375732396E-3</v>
+        <v>4.2402744293212804E-3</v>
       </c>
       <c r="Q12" t="s">
-        <v>166</v>
+        <v>47</v>
       </c>
       <c r="R12">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S12" t="s">
-        <v>167</v>
+        <v>49</v>
       </c>
       <c r="T12">
-        <v>0.10184775000016</v>
+        <v>0.109177917000124</v>
       </c>
       <c r="U12">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X12" t="s">
-        <v>167</v>
+        <v>49</v>
       </c>
       <c r="Y12">
-        <v>0.69615558399982502</v>
+        <v>0.46063137500004803</v>
       </c>
       <c r="Z12">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AA12">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="s">
-        <v>250</v>
+        <v>49</v>
       </c>
       <c r="AD12">
-        <v>3.37205650099986</v>
+        <v>1.8838435839998</v>
       </c>
       <c r="AE12">
         <v>33</v>
@@ -3304,292 +3297,286 @@
         <v>0</v>
       </c>
       <c r="AH12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="B13">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C13">
         <v>40</v>
       </c>
       <c r="D13">
-        <v>5505.72230434417</v>
-      </c>
-      <c r="E13" t="s">
-        <v>173</v>
-      </c>
-      <c r="F13">
-        <v>35</v>
+        <v>86400.874973535494</v>
       </c>
       <c r="G13">
-        <v>580.17795109748795</v>
+        <v>70.089067459106403</v>
       </c>
       <c r="H13" t="s">
-        <v>173</v>
+        <v>50</v>
       </c>
       <c r="I13">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J13">
-        <v>479.90765690803499</v>
+        <v>230.956568717956</v>
       </c>
       <c r="K13" t="s">
-        <v>174</v>
+        <v>51</v>
       </c>
       <c r="L13">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M13">
-        <v>86400.134572505907</v>
+        <v>86400.140295505495</v>
       </c>
       <c r="P13">
-        <v>5.4419040679931597E-3</v>
+        <v>5.2533149719238203E-3</v>
       </c>
       <c r="Q13" t="s">
-        <v>175</v>
+        <v>52</v>
       </c>
       <c r="R13">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="S13" t="s">
-        <v>176</v>
+        <v>53</v>
       </c>
       <c r="T13">
-        <v>0.103053875000114</v>
+        <v>0.360892499999863</v>
       </c>
       <c r="U13">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="V13">
+        <v>-10</v>
+      </c>
+      <c r="W13">
+        <v>-8</v>
+      </c>
+      <c r="X13" t="s">
+        <v>216</v>
+      </c>
+      <c r="Y13">
+        <v>1.00651333400037</v>
+      </c>
+      <c r="Z13">
+        <v>37</v>
+      </c>
+      <c r="AA13">
         <v>-1</v>
-      </c>
-      <c r="W13">
-        <v>2</v>
-      </c>
-      <c r="X13" t="s">
-        <v>229</v>
-      </c>
-      <c r="Y13">
-        <v>0.50271679199977304</v>
-      </c>
-      <c r="Z13">
-        <v>33</v>
-      </c>
-      <c r="AA13">
-        <v>-2</v>
       </c>
       <c r="AB13">
         <v>1</v>
       </c>
       <c r="AC13" t="s">
-        <v>176</v>
+        <v>241</v>
       </c>
       <c r="AD13">
-        <v>3.8542224180000599</v>
+        <v>3.8565233350000199</v>
       </c>
       <c r="AE13">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AF13">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AH13">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14">
         <v>40</v>
       </c>
       <c r="D14">
-        <v>271.16198706626801</v>
+        <v>58.451675891876199</v>
       </c>
       <c r="E14" t="s">
-        <v>180</v>
+        <v>54</v>
       </c>
       <c r="F14">
         <v>32</v>
       </c>
       <c r="G14">
-        <v>94.3208456039428</v>
+        <v>22.211640119552602</v>
       </c>
       <c r="H14" t="s">
-        <v>180</v>
+        <v>55</v>
       </c>
       <c r="I14">
-        <v>32</v>
+        <v>31.999999999999901</v>
       </c>
       <c r="J14">
-        <v>332.61604619026099</v>
+        <v>173.92218637466399</v>
       </c>
       <c r="K14" t="s">
-        <v>180</v>
+        <v>56</v>
       </c>
       <c r="L14">
         <v>32</v>
       </c>
       <c r="M14">
-        <v>86400.134548902497</v>
+        <v>86400.126599073395</v>
       </c>
       <c r="P14">
-        <v>4.8720836639404297E-3</v>
+        <v>4.5175552368164002E-3</v>
       </c>
       <c r="Q14" t="s">
-        <v>180</v>
+        <v>57</v>
       </c>
       <c r="R14">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S14" t="s">
-        <v>181</v>
+        <v>58</v>
       </c>
       <c r="T14">
-        <v>0.104308082999978</v>
+        <v>0.16163216699987901</v>
       </c>
       <c r="U14">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>-0.999999999999996</v>
       </c>
       <c r="W14">
         <v>0</v>
       </c>
       <c r="X14" t="s">
-        <v>181</v>
+        <v>217</v>
       </c>
       <c r="Y14">
-        <v>0.544640124999205</v>
+        <v>0.70187862500006304</v>
       </c>
       <c r="Z14">
         <v>32</v>
       </c>
-      <c r="AA14">
-        <v>0</v>
+      <c r="AA14" s="1">
+        <v>3.5527136788005001E-15</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC14" t="s">
-        <v>181</v>
+        <v>217</v>
       </c>
       <c r="AD14">
-        <v>2.4789781680001299</v>
+        <v>1.63539791699986</v>
       </c>
       <c r="AE14">
         <v>32</v>
       </c>
-      <c r="AF14">
-        <v>0</v>
+      <c r="AF14" s="1">
+        <v>3.5527136788005001E-15</v>
       </c>
       <c r="AG14">
         <v>0</v>
       </c>
       <c r="AH14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="B15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C15">
         <v>40</v>
       </c>
       <c r="D15">
-        <v>20.868867158889699</v>
+        <v>850.74028325080803</v>
       </c>
       <c r="E15" t="s">
-        <v>201</v>
+        <v>59</v>
       </c>
       <c r="F15">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G15">
-        <v>5634.1728641986801</v>
+        <v>88.225219011306706</v>
       </c>
       <c r="H15" t="s">
-        <v>202</v>
+        <v>60</v>
       </c>
       <c r="I15">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J15">
-        <v>1068.1284990310601</v>
+        <v>341.805687904357</v>
       </c>
       <c r="K15" t="s">
-        <v>201</v>
+        <v>61</v>
       </c>
       <c r="L15">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="M15">
-        <v>86400.086030006394</v>
+        <v>86400.125456094698</v>
       </c>
       <c r="P15">
-        <v>4.53543663024902E-3</v>
+        <v>5.1207542419433498E-3</v>
       </c>
       <c r="Q15" t="s">
-        <v>203</v>
+        <v>62</v>
       </c>
       <c r="R15">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="S15" t="s">
-        <v>204</v>
+        <v>63</v>
       </c>
       <c r="T15">
-        <v>0.104485040999861</v>
+        <v>0.13082475000010099</v>
       </c>
       <c r="U15">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="V15">
         <v>0</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="X15" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="Y15">
-        <v>0.34610658299970898</v>
+        <v>0.81035420900025201</v>
       </c>
       <c r="Z15">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AC15" t="s">
-        <v>204</v>
+        <v>242</v>
       </c>
       <c r="AD15">
-        <v>1.33293304200014</v>
+        <v>3.97558945999935</v>
       </c>
       <c r="AE15">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="AF15">
         <v>0</v>
@@ -3598,96 +3585,96 @@
         <v>0</v>
       </c>
       <c r="AH15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="B16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C16">
         <v>40</v>
       </c>
       <c r="D16">
-        <v>79.188139438629094</v>
+        <v>847.00700283050503</v>
       </c>
       <c r="E16" t="s">
-        <v>162</v>
+        <v>64</v>
       </c>
       <c r="F16">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="G16">
-        <v>610.82811737060501</v>
+        <v>58.091557264328003</v>
       </c>
       <c r="H16" t="s">
-        <v>163</v>
+        <v>64</v>
       </c>
       <c r="I16">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="J16">
-        <v>276.89593887329102</v>
+        <v>197.25004124641401</v>
       </c>
       <c r="K16" t="s">
-        <v>163</v>
+        <v>64</v>
       </c>
       <c r="L16">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="M16">
-        <v>86400.126035213398</v>
+        <v>86400.126175403595</v>
       </c>
       <c r="P16">
-        <v>6.1039924621581997E-3</v>
+        <v>5.2807331085205E-3</v>
       </c>
       <c r="Q16" t="s">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="R16">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="S16" t="s">
-        <v>164</v>
+        <v>66</v>
       </c>
       <c r="T16">
-        <v>0.105333333000089</v>
+        <v>0.22201533399993401</v>
       </c>
       <c r="U16">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="X16" t="s">
-        <v>164</v>
+        <v>219</v>
       </c>
       <c r="Y16">
-        <v>0.50584537499980797</v>
+        <v>1.1471546250004301</v>
       </c>
       <c r="Z16">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="s">
-        <v>164</v>
+        <v>219</v>
       </c>
       <c r="AD16">
-        <v>1.0728722090006999</v>
+        <v>3.39485687699925</v>
       </c>
       <c r="AE16">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AF16">
         <v>0</v>
@@ -3696,110 +3683,110 @@
         <v>0</v>
       </c>
       <c r="AH16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17">
         <v>40</v>
       </c>
       <c r="D17">
-        <v>1175.05269384384</v>
+        <v>1160.6931722164099</v>
       </c>
       <c r="E17" t="s">
-        <v>113</v>
+        <v>67</v>
       </c>
       <c r="F17">
         <v>36</v>
       </c>
       <c r="G17">
-        <v>141.49965786933899</v>
+        <v>60.158497571945098</v>
       </c>
       <c r="H17" t="s">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="I17">
         <v>36</v>
       </c>
       <c r="J17">
-        <v>477.19279837608298</v>
+        <v>220.47335624694799</v>
       </c>
       <c r="K17" t="s">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="L17">
         <v>36</v>
       </c>
       <c r="M17">
-        <v>86400.130617856907</v>
+        <v>86400.164609908999</v>
       </c>
       <c r="P17">
-        <v>5.4810047149658203E-3</v>
+        <v>5.1751136779785104E-3</v>
       </c>
       <c r="Q17" t="s">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="R17">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S17" t="s">
-        <v>117</v>
+        <v>69</v>
       </c>
       <c r="T17">
-        <v>0.10916200000019601</v>
+        <v>0.101051209000161</v>
       </c>
       <c r="U17">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X17" t="s">
-        <v>117</v>
+        <v>69</v>
       </c>
       <c r="Y17">
-        <v>0.79457316700063496</v>
+        <v>0.438611583000238</v>
       </c>
       <c r="Z17">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AA17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="s">
-        <v>117</v>
+        <v>69</v>
       </c>
       <c r="AD17">
-        <v>3.4563811259995401</v>
+        <v>1.18862187499962</v>
       </c>
       <c r="AE17">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AF17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AH17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B18">
         <v>4</v>
@@ -3808,52 +3795,52 @@
         <v>40</v>
       </c>
       <c r="D18">
-        <v>236.19271969795199</v>
-      </c>
-      <c r="E18" t="s">
-        <v>47</v>
-      </c>
-      <c r="F18">
-        <v>33</v>
+        <v>86400.324173450397</v>
       </c>
       <c r="G18">
-        <v>51.336097240447998</v>
+        <v>76.000017881393404</v>
       </c>
       <c r="H18" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="I18">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J18">
-        <v>230.964210748672</v>
+        <v>132.477592945098</v>
       </c>
       <c r="K18" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="L18">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="M18">
-        <v>86400.596881627993</v>
+        <v>47.098084926605203</v>
+      </c>
+      <c r="N18" t="s">
+        <v>72</v>
+      </c>
+      <c r="O18">
+        <v>39</v>
       </c>
       <c r="P18">
-        <v>4.2402744293212804E-3</v>
+        <v>6.5302848815917899E-3</v>
       </c>
       <c r="Q18" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="R18">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="S18" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="T18">
-        <v>0.109177917000124</v>
+        <v>0.147897666999597</v>
       </c>
       <c r="U18">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="V18">
         <v>0</v>
@@ -3862,13 +3849,13 @@
         <v>0</v>
       </c>
       <c r="X18" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="Y18">
-        <v>0.46063137500004803</v>
+        <v>0.63420491699980597</v>
       </c>
       <c r="Z18">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="AA18">
         <v>0</v>
@@ -3877,13 +3864,13 @@
         <v>0</v>
       </c>
       <c r="AC18" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="AD18">
-        <v>1.8838435839998</v>
+        <v>3.9922276269999202</v>
       </c>
       <c r="AE18">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="AF18">
         <v>0</v>
@@ -3895,93 +3882,93 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19">
         <v>40</v>
       </c>
       <c r="D19">
-        <v>210.87740945816</v>
+        <v>78285.793434858293</v>
       </c>
       <c r="E19" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="F19">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G19">
-        <v>162.65208864211999</v>
+        <v>77.328538656234699</v>
       </c>
       <c r="H19" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="I19">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J19">
-        <v>318.648909568786</v>
+        <v>224.450894832611</v>
       </c>
       <c r="K19" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="L19">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="M19">
-        <v>86400.133867740602</v>
+        <v>86400.140725135803</v>
       </c>
       <c r="P19">
-        <v>4.4388771057128898E-3</v>
+        <v>5.2385330200195304E-3</v>
       </c>
       <c r="Q19" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="R19">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="S19" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="T19">
-        <v>0.109529583000039</v>
+        <v>0.32934462499997602</v>
       </c>
       <c r="U19">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="W19">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="X19" t="s">
-        <v>91</v>
+        <v>220</v>
       </c>
       <c r="Y19">
-        <v>0.33714795800005898</v>
+        <v>1.09348520799994</v>
       </c>
       <c r="Z19">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC19" t="s">
-        <v>91</v>
+        <v>220</v>
       </c>
       <c r="AD19">
-        <v>0.97163041700059605</v>
+        <v>3.1117815429997702</v>
       </c>
       <c r="AE19">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="AF19">
         <v>0</v>
@@ -3990,306 +3977,306 @@
         <v>0</v>
       </c>
       <c r="AH19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20">
         <v>40</v>
       </c>
       <c r="D20">
-        <v>4296.8034508228302</v>
+        <v>6526.2341415882102</v>
       </c>
       <c r="E20" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="F20">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G20">
-        <v>44.4875199794769</v>
+        <v>64.794146537780705</v>
       </c>
       <c r="H20" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="I20">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J20">
-        <v>188.74511742591801</v>
+        <v>234.16041851043701</v>
       </c>
       <c r="K20" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="L20">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M20">
-        <v>86400.489632844896</v>
+        <v>86400.141325473698</v>
       </c>
       <c r="P20">
-        <v>5.0759315490722604E-3</v>
+        <v>4.3635368347167899E-3</v>
       </c>
       <c r="Q20" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="R20">
         <v>34</v>
       </c>
       <c r="S20" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="T20">
-        <v>0.110329999999976</v>
+        <v>0.195492166999883</v>
       </c>
       <c r="U20">
-        <v>34</v>
-      </c>
-      <c r="V20">
-        <v>0</v>
+        <v>35</v>
+      </c>
+      <c r="V20" s="1">
+        <v>-7.1054273576010003E-15</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="Y20">
-        <v>0.43649625000034498</v>
+        <v>1.3690103760000001</v>
       </c>
       <c r="Z20">
-        <v>34</v>
-      </c>
-      <c r="AA20">
-        <v>0</v>
+        <v>35</v>
+      </c>
+      <c r="AA20" s="1">
+        <v>-7.1054273576010003E-15</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC20" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="AD20">
-        <v>1.4178213759996601</v>
+        <v>5.68862400299985</v>
       </c>
       <c r="AE20">
-        <v>34</v>
-      </c>
-      <c r="AF20">
-        <v>0</v>
+        <v>35</v>
+      </c>
+      <c r="AF20" s="1">
+        <v>-7.1054273576010003E-15</v>
       </c>
       <c r="AG20">
         <v>0</v>
       </c>
       <c r="AH20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="B21">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C21">
         <v>40</v>
       </c>
       <c r="D21">
-        <v>4.9631543159484801</v>
+        <v>759.06535601615894</v>
       </c>
       <c r="E21" t="s">
-        <v>157</v>
+        <v>83</v>
       </c>
       <c r="F21">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G21">
-        <v>6913.6652741432099</v>
+        <v>912.31764340400696</v>
       </c>
       <c r="H21" t="s">
-        <v>158</v>
+        <v>84</v>
       </c>
       <c r="I21">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J21">
-        <v>546.080072641372</v>
+        <v>540.48723745346001</v>
       </c>
       <c r="K21" t="s">
-        <v>159</v>
+        <v>85</v>
       </c>
       <c r="L21">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="M21">
-        <v>86400.127148866595</v>
+        <v>86400.132619380907</v>
       </c>
       <c r="P21">
-        <v>5.1782131195068299E-3</v>
+        <v>4.8832893371581997E-3</v>
       </c>
       <c r="Q21" t="s">
-        <v>160</v>
+        <v>86</v>
       </c>
       <c r="R21">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="S21" t="s">
-        <v>161</v>
+        <v>87</v>
       </c>
       <c r="T21">
-        <v>0.11649966699997</v>
+        <v>0.10059033400011599</v>
       </c>
       <c r="U21">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W21">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="X21" t="s">
-        <v>161</v>
+        <v>87</v>
       </c>
       <c r="Y21">
-        <v>0.49047770899960502</v>
+        <v>0.36835916700056198</v>
       </c>
       <c r="Z21">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AB21">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="s">
-        <v>161</v>
+        <v>87</v>
       </c>
       <c r="AD21">
-        <v>1.0256034170006301</v>
+        <v>0.92678079200049901</v>
       </c>
       <c r="AE21">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AH21">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C22">
         <v>40</v>
       </c>
       <c r="D22">
-        <v>98.0358052253723</v>
+        <v>210.87740945816</v>
       </c>
       <c r="E22" t="s">
-        <v>146</v>
+        <v>88</v>
       </c>
       <c r="F22">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G22">
-        <v>1499.5055146217301</v>
+        <v>162.65208864211999</v>
       </c>
       <c r="H22" t="s">
-        <v>147</v>
+        <v>88</v>
       </c>
       <c r="I22">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J22">
-        <v>453.13620591163601</v>
+        <v>318.648909568786</v>
       </c>
       <c r="K22" t="s">
-        <v>147</v>
+        <v>89</v>
       </c>
       <c r="L22">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="M22">
-        <v>86400.137974739002</v>
+        <v>86400.133867740602</v>
       </c>
       <c r="P22">
-        <v>5.1372051239013602E-3</v>
+        <v>4.4388771057128898E-3</v>
       </c>
       <c r="Q22" t="s">
-        <v>148</v>
+        <v>90</v>
       </c>
       <c r="R22">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="S22" t="s">
-        <v>149</v>
+        <v>91</v>
       </c>
       <c r="T22">
-        <v>0.117617542000061</v>
+        <v>0.109529583000039</v>
       </c>
       <c r="U22">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="V22">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X22" t="s">
-        <v>227</v>
+        <v>91</v>
       </c>
       <c r="Y22">
-        <v>0.38466891700045303</v>
+        <v>0.33714795800005898</v>
       </c>
       <c r="Z22">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="AA22">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC22" t="s">
-        <v>249</v>
+        <v>91</v>
       </c>
       <c r="AD22">
-        <v>0.81504812500043</v>
+        <v>0.97163041700059605</v>
       </c>
       <c r="AE22">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="AF22">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AH22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B23">
         <v>5</v>
@@ -4298,82 +4285,82 @@
         <v>40</v>
       </c>
       <c r="D23">
-        <v>147.89943647384601</v>
+        <v>7105.1666977405503</v>
       </c>
       <c r="E23" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="F23">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G23">
-        <v>59.577576637268002</v>
+        <v>57.698698759078901</v>
       </c>
       <c r="H23" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="I23">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J23">
-        <v>278.319145917892</v>
+        <v>251.577482938766</v>
       </c>
       <c r="K23" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="L23">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="M23">
-        <v>86400.134596109303</v>
+        <v>86400.135037422093</v>
       </c>
       <c r="P23">
-        <v>4.8899650573730399E-3</v>
+        <v>5.1634311676025304E-3</v>
       </c>
       <c r="Q23" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="R23">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="S23" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="T23">
-        <v>0.12346158399986901</v>
+        <v>0.14005504099986801</v>
       </c>
       <c r="U23">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X23" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="Y23">
-        <v>0.52061320800021305</v>
+        <v>1.0972684180005601</v>
       </c>
       <c r="Z23">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AB23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC23" t="s">
-        <v>120</v>
+        <v>243</v>
       </c>
       <c r="AD23">
-        <v>1.1719093760002499</v>
+        <v>7.6424404210001704</v>
       </c>
       <c r="AE23">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="AF23">
         <v>0</v>
@@ -4385,9 +4372,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B24">
         <v>5</v>
@@ -4396,82 +4383,82 @@
         <v>40</v>
       </c>
       <c r="D24">
-        <v>5.8123471736907897</v>
+        <v>729.35242557525601</v>
       </c>
       <c r="E24" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="F24">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G24">
-        <v>87.840272665023804</v>
+        <v>58.242346525192197</v>
       </c>
       <c r="H24" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="I24">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J24">
-        <v>317.97413492202702</v>
+        <v>291.66989302635102</v>
       </c>
       <c r="K24" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="L24">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="M24">
-        <v>86400.127450704502</v>
+        <v>86400.160304784702</v>
       </c>
       <c r="P24">
-        <v>5.0079822540283203E-3</v>
+        <v>5.1820278167724601E-3</v>
       </c>
       <c r="Q24" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="R24">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="S24" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="T24">
-        <v>0.123655457999575</v>
+        <v>0.39884087499967702</v>
       </c>
       <c r="U24">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X24" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="Y24">
-        <v>0.232836958000007</v>
+        <v>1.5459725010005001</v>
       </c>
       <c r="Z24">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AA24">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC24" t="s">
-        <v>245</v>
+        <v>101</v>
       </c>
       <c r="AD24">
-        <v>0.96458545899986303</v>
+        <v>9.5797322550006303</v>
       </c>
       <c r="AE24">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="AF24">
         <v>0</v>
@@ -4480,96 +4467,96 @@
         <v>0</v>
       </c>
       <c r="AH24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C25">
         <v>40</v>
       </c>
       <c r="D25">
-        <v>434.91103124618502</v>
+        <v>158.90096259117101</v>
       </c>
       <c r="E25" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
       <c r="F25">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G25">
-        <v>51.784494161605799</v>
+        <v>91.672548770904498</v>
       </c>
       <c r="H25" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="I25">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J25">
-        <v>268.26836252212502</v>
+        <v>319.44056868553099</v>
       </c>
       <c r="K25" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="L25">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="M25">
-        <v>86400.137657165498</v>
+        <v>86400.131307125004</v>
       </c>
       <c r="P25">
-        <v>5.3925514221191398E-3</v>
+        <v>5.7320594787597604E-3</v>
       </c>
       <c r="Q25" t="s">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="R25">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="S25" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="T25">
-        <v>0.129812333000245</v>
+        <v>0.13351787500005199</v>
       </c>
       <c r="U25">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="W25">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="X25" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="Y25">
-        <v>1.0161245420003899</v>
+        <v>0.85035683399928497</v>
       </c>
       <c r="Z25">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA25">
         <v>0</v>
       </c>
       <c r="AB25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC25" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="AD25">
-        <v>2.1120852509993702</v>
+        <v>1.73933054200006</v>
       </c>
       <c r="AE25">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF25">
         <v>0</v>
@@ -4578,96 +4565,102 @@
         <v>0</v>
       </c>
       <c r="AH25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26">
         <v>40</v>
       </c>
       <c r="D26">
-        <v>850.74028325080803</v>
+        <v>2010.4343097209901</v>
       </c>
       <c r="E26" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="F26">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G26">
-        <v>88.225219011306706</v>
+        <v>65.932975530624304</v>
       </c>
       <c r="H26" t="s">
-        <v>60</v>
+        <v>107</v>
       </c>
       <c r="I26">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J26">
-        <v>341.805687904357</v>
+        <v>297.85724782943697</v>
       </c>
       <c r="K26" t="s">
-        <v>61</v>
+        <v>107</v>
       </c>
       <c r="L26">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M26">
-        <v>86400.125456094698</v>
+        <v>34203.160275936098</v>
+      </c>
+      <c r="N26" t="s">
+        <v>107</v>
+      </c>
+      <c r="O26">
+        <v>34</v>
       </c>
       <c r="P26">
-        <v>5.1207542419433498E-3</v>
+        <v>4.5621395111083898E-3</v>
       </c>
       <c r="Q26" t="s">
-        <v>62</v>
+        <v>107</v>
       </c>
       <c r="R26">
         <v>34</v>
       </c>
       <c r="S26" t="s">
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="T26">
-        <v>0.13082475000010099</v>
+        <v>7.3529333999886107E-2</v>
       </c>
       <c r="U26">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V26">
         <v>0</v>
       </c>
       <c r="W26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X26" t="s">
-        <v>218</v>
+        <v>108</v>
       </c>
       <c r="Y26">
-        <v>0.81035420900025201</v>
+        <v>0.52385645800040903</v>
       </c>
       <c r="Z26">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA26">
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="s">
-        <v>242</v>
+        <v>108</v>
       </c>
       <c r="AD26">
-        <v>3.97558945999935</v>
+        <v>1.1891566680005701</v>
       </c>
       <c r="AE26">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AF26">
         <v>0</v>
@@ -4676,96 +4669,96 @@
         <v>0</v>
       </c>
       <c r="AH26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="B27">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C27">
         <v>40</v>
       </c>
       <c r="D27">
-        <v>24.768089056015</v>
+        <v>2330.9193391799899</v>
       </c>
       <c r="E27" t="s">
-        <v>196</v>
+        <v>109</v>
       </c>
       <c r="F27">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="G27">
-        <v>17601.845165967901</v>
+        <v>58.3836863040924</v>
       </c>
       <c r="H27" t="s">
-        <v>197</v>
+        <v>110</v>
       </c>
       <c r="I27">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J27">
-        <v>1496.15870833396</v>
+        <v>181.586270332336</v>
       </c>
       <c r="K27" t="s">
-        <v>198</v>
+        <v>109</v>
       </c>
       <c r="L27">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="M27">
-        <v>86400.219609498905</v>
+        <v>86400.129125595093</v>
       </c>
       <c r="P27">
-        <v>4.7314167022705E-3</v>
+        <v>6.0391426086425703E-3</v>
       </c>
       <c r="Q27" t="s">
-        <v>199</v>
+        <v>111</v>
       </c>
       <c r="R27">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="S27" t="s">
-        <v>200</v>
+        <v>112</v>
       </c>
       <c r="T27">
-        <v>0.13343433399995699</v>
+        <v>0.162366374999692</v>
       </c>
       <c r="U27">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X27" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="Y27">
-        <v>0.47714245899987801</v>
+        <v>1.19237250100013</v>
       </c>
       <c r="Z27">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AB27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC27" t="s">
-        <v>200</v>
+        <v>244</v>
       </c>
       <c r="AD27">
-        <v>1.4057622509999399</v>
+        <v>5.5275429610001003</v>
       </c>
       <c r="AE27">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AF27">
         <v>0</v>
@@ -4777,9 +4770,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B28">
         <v>5</v>
@@ -4788,279 +4781,279 @@
         <v>40</v>
       </c>
       <c r="D28">
-        <v>158.90096259117101</v>
+        <v>1175.05269384384</v>
       </c>
       <c r="E28" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="F28">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G28">
-        <v>91.672548770904498</v>
+        <v>141.49965786933899</v>
       </c>
       <c r="H28" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="I28">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J28">
-        <v>319.44056868553099</v>
+        <v>477.19279837608298</v>
       </c>
       <c r="K28" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="L28">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M28">
-        <v>86400.131307125004</v>
+        <v>86400.130617856907</v>
       </c>
       <c r="P28">
-        <v>5.7320594787597604E-3</v>
+        <v>5.4810047149658203E-3</v>
       </c>
       <c r="Q28" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="R28">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S28" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="T28">
-        <v>0.13351787500005199</v>
+        <v>0.10916200000019601</v>
       </c>
       <c r="U28">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="V28">
-        <v>-10</v>
+        <v>-1</v>
       </c>
       <c r="W28">
-        <v>-7</v>
+        <v>2</v>
       </c>
       <c r="X28" t="s">
-        <v>222</v>
+        <v>117</v>
       </c>
       <c r="Y28">
-        <v>0.85035683399928497</v>
+        <v>0.79457316700063496</v>
       </c>
       <c r="Z28">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AB28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC28" t="s">
-        <v>222</v>
+        <v>117</v>
       </c>
       <c r="AD28">
-        <v>1.73933054200006</v>
+        <v>3.4563811259995401</v>
       </c>
       <c r="AE28">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AH28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="B29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C29">
         <v>40</v>
       </c>
       <c r="D29">
-        <v>712.73984003067005</v>
+        <v>147.89943647384601</v>
       </c>
       <c r="E29" t="s">
-        <v>168</v>
+        <v>118</v>
       </c>
       <c r="F29">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G29">
-        <v>1518.63394331932</v>
+        <v>59.577576637268002</v>
       </c>
       <c r="H29" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="I29">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J29">
-        <v>707.79996132850601</v>
+        <v>278.319145917892</v>
       </c>
       <c r="K29" t="s">
-        <v>170</v>
+        <v>118</v>
       </c>
       <c r="L29">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M29">
-        <v>86400.211915969805</v>
+        <v>86400.134596109303</v>
       </c>
       <c r="P29">
-        <v>5.31005859375E-3</v>
+        <v>4.8899650573730399E-3</v>
       </c>
       <c r="Q29" t="s">
-        <v>171</v>
+        <v>119</v>
       </c>
       <c r="R29">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="S29" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="T29">
-        <v>0.134515959000054</v>
+        <v>0.12346158399986901</v>
       </c>
       <c r="U29">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X29" t="s">
-        <v>228</v>
+        <v>120</v>
       </c>
       <c r="Y29">
-        <v>0.85145383400049401</v>
+        <v>0.52061320800021305</v>
       </c>
       <c r="Z29">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="AA29">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC29" t="s">
-        <v>228</v>
+        <v>120</v>
       </c>
       <c r="AD29">
-        <v>2.5544875010000299</v>
+        <v>1.1719093760002499</v>
       </c>
       <c r="AE29">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="AF29">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AH29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="B30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C30">
         <v>40</v>
       </c>
       <c r="D30">
-        <v>50.2884037494659</v>
+        <v>5.8123471736907897</v>
       </c>
       <c r="E30" t="s">
-        <v>187</v>
+        <v>121</v>
       </c>
       <c r="F30">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G30">
-        <v>89.7342205047607</v>
+        <v>87.840272665023804</v>
       </c>
       <c r="H30" t="s">
-        <v>188</v>
+        <v>122</v>
       </c>
       <c r="I30">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J30">
-        <v>544.07556653022698</v>
+        <v>317.97413492202702</v>
       </c>
       <c r="K30" t="s">
-        <v>187</v>
+        <v>123</v>
       </c>
       <c r="L30">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M30">
-        <v>86400.1261193752</v>
+        <v>86400.127450704502</v>
       </c>
       <c r="P30">
-        <v>5.8310031890869097E-3</v>
+        <v>5.0079822540283203E-3</v>
       </c>
       <c r="Q30" t="s">
-        <v>189</v>
+        <v>124</v>
       </c>
       <c r="R30">
+        <v>32</v>
+      </c>
+      <c r="S30" t="s">
+        <v>125</v>
+      </c>
+      <c r="T30">
+        <v>0.123655457999575</v>
+      </c>
+      <c r="U30">
+        <v>32</v>
+      </c>
+      <c r="V30">
+        <v>-1</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30" t="s">
+        <v>224</v>
+      </c>
+      <c r="Y30">
+        <v>0.232836958000007</v>
+      </c>
+      <c r="Z30">
+        <v>32</v>
+      </c>
+      <c r="AA30">
+        <v>-1</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>245</v>
+      </c>
+      <c r="AD30">
+        <v>0.96458545899986303</v>
+      </c>
+      <c r="AE30">
         <v>33</v>
       </c>
-      <c r="S30" t="s">
-        <v>190</v>
-      </c>
-      <c r="T30">
-        <v>0.13723908300016699</v>
-      </c>
-      <c r="U30">
-        <v>33</v>
-      </c>
-      <c r="V30">
-        <v>-2</v>
-      </c>
-      <c r="W30">
-        <v>0</v>
-      </c>
-      <c r="X30" t="s">
-        <v>230</v>
-      </c>
-      <c r="Y30">
-        <v>1.22124062599959</v>
-      </c>
-      <c r="Z30">
-        <v>35</v>
-      </c>
-      <c r="AA30">
-        <v>0</v>
-      </c>
-      <c r="AB30">
-        <v>2</v>
-      </c>
-      <c r="AC30" t="s">
-        <v>230</v>
-      </c>
-      <c r="AD30">
-        <v>5.3473507110002103</v>
-      </c>
-      <c r="AE30">
-        <v>35</v>
-      </c>
       <c r="AF30">
         <v>0</v>
       </c>
@@ -5068,12 +5061,12 @@
         <v>0</v>
       </c>
       <c r="AH30">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B31">
         <v>5</v>
@@ -5082,82 +5075,82 @@
         <v>40</v>
       </c>
       <c r="D31">
-        <v>7105.1666977405503</v>
+        <v>805.73928236961297</v>
       </c>
       <c r="E31" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="F31">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G31">
-        <v>57.698698759078901</v>
+        <v>58.891531467437702</v>
       </c>
       <c r="H31" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="I31">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="J31">
-        <v>251.577482938766</v>
+        <v>259.028136491775</v>
       </c>
       <c r="K31" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="L31">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="M31">
-        <v>86400.135037422093</v>
+        <v>86400.1880934238</v>
       </c>
       <c r="P31">
-        <v>5.1634311676025304E-3</v>
+        <v>4.7945976257324201E-3</v>
       </c>
       <c r="Q31" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="R31">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="S31" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="T31">
-        <v>0.14005504099986801</v>
+        <v>0.169992041000114</v>
       </c>
       <c r="U31">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X31" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="Y31">
-        <v>1.0972684180005601</v>
+        <v>0.700133125999855</v>
       </c>
       <c r="Z31">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="AA31">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="s">
-        <v>243</v>
+        <v>127</v>
       </c>
       <c r="AD31">
-        <v>7.6424404210001704</v>
+        <v>1.6987882510002199</v>
       </c>
       <c r="AE31">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AF31">
         <v>0</v>
@@ -5166,96 +5159,96 @@
         <v>0</v>
       </c>
       <c r="AH31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="B32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32">
         <v>40</v>
       </c>
       <c r="D32">
-        <v>291.48174500465302</v>
+        <v>1909.8805825710201</v>
       </c>
       <c r="E32" t="s">
-        <v>182</v>
+        <v>128</v>
       </c>
       <c r="F32">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="G32">
-        <v>213.53333497047399</v>
+        <v>52.664197683334301</v>
       </c>
       <c r="H32" t="s">
-        <v>183</v>
+        <v>129</v>
       </c>
       <c r="I32">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="J32">
-        <v>478.408534049987</v>
+        <v>176.476865291595</v>
       </c>
       <c r="K32" t="s">
-        <v>184</v>
+        <v>130</v>
       </c>
       <c r="L32">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="M32">
-        <v>86400.129339218096</v>
+        <v>86400.145117759705</v>
       </c>
       <c r="P32">
-        <v>5.0356388092040998E-3</v>
+        <v>6.1647891998290998E-3</v>
       </c>
       <c r="Q32" t="s">
-        <v>185</v>
+        <v>131</v>
       </c>
       <c r="R32">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="S32" t="s">
-        <v>186</v>
+        <v>132</v>
       </c>
       <c r="T32">
-        <v>0.14090329200007501</v>
+        <v>0.23984020799980499</v>
       </c>
       <c r="U32">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="V32">
         <v>0</v>
       </c>
       <c r="W32">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X32" t="s">
-        <v>186</v>
+        <v>132</v>
       </c>
       <c r="Y32">
-        <v>0.50693925000086804</v>
+        <v>1.54557029199986</v>
       </c>
       <c r="Z32">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AA32">
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AC32" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="AD32">
-        <v>1.01202449999982</v>
+        <v>10.299458254000401</v>
       </c>
       <c r="AE32">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AF32">
         <v>0</v>
@@ -5264,161 +5257,161 @@
         <v>0</v>
       </c>
       <c r="AH32">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="B33">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C33">
         <v>40</v>
       </c>
       <c r="D33">
-        <v>453.44278931617703</v>
+        <v>907.86760544776905</v>
       </c>
       <c r="E33" t="s">
+        <v>133</v>
+      </c>
+      <c r="F33">
+        <v>34</v>
+      </c>
+      <c r="G33">
+        <v>79.067918539047199</v>
+      </c>
+      <c r="H33" t="s">
+        <v>134</v>
+      </c>
+      <c r="I33">
+        <v>34</v>
+      </c>
+      <c r="J33">
+        <v>293.41959142684902</v>
+      </c>
+      <c r="K33" t="s">
+        <v>135</v>
+      </c>
+      <c r="L33">
+        <v>34</v>
+      </c>
+      <c r="M33">
+        <v>86400.082375526399</v>
+      </c>
+      <c r="P33">
+        <v>6.0026645660400304E-3</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>136</v>
+      </c>
+      <c r="R33">
+        <v>33</v>
+      </c>
+      <c r="S33" t="s">
+        <v>137</v>
+      </c>
+      <c r="T33">
+        <v>0.39023537499997402</v>
+      </c>
+      <c r="U33">
         <v>18</v>
       </c>
-      <c r="F33">
+      <c r="V33">
+        <v>-16</v>
+      </c>
+      <c r="W33">
+        <v>-15</v>
+      </c>
+      <c r="X33" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y33">
+        <v>0.82609883400073103</v>
+      </c>
+      <c r="Z33">
+        <v>34</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <v>1</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>247</v>
+      </c>
+      <c r="AD33">
+        <v>2.0154344180000399</v>
+      </c>
+      <c r="AE33">
+        <v>34</v>
+      </c>
+      <c r="AF33">
+        <v>0</v>
+      </c>
+      <c r="AG33">
+        <v>0</v>
+      </c>
+      <c r="AH33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A34">
         <v>33</v>
       </c>
-      <c r="G33">
-        <v>47.695116281509399</v>
-      </c>
-      <c r="H33" t="s">
-        <v>19</v>
-      </c>
-      <c r="I33">
-        <v>33</v>
-      </c>
-      <c r="J33">
-        <v>196.83315134048399</v>
-      </c>
-      <c r="K33" t="s">
-        <v>20</v>
-      </c>
-      <c r="L33">
-        <v>33</v>
-      </c>
-      <c r="M33">
-        <v>86400.139185190201</v>
-      </c>
-      <c r="P33">
-        <v>5.6414604187011701E-3</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>21</v>
-      </c>
-      <c r="R33">
-        <v>31</v>
-      </c>
-      <c r="S33" t="s">
-        <v>22</v>
-      </c>
-      <c r="T33">
-        <v>0.14114279199975499</v>
-      </c>
-      <c r="U33">
-        <v>33</v>
-      </c>
-      <c r="V33">
-        <v>0</v>
-      </c>
-      <c r="W33">
-        <v>2</v>
-      </c>
-      <c r="X33" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y33">
-        <v>0.39363883399983002</v>
-      </c>
-      <c r="Z33">
-        <v>33</v>
-      </c>
-      <c r="AA33">
-        <v>0</v>
-      </c>
-      <c r="AB33">
-        <v>2</v>
-      </c>
-      <c r="AC33" t="s">
-        <v>238</v>
-      </c>
-      <c r="AD33">
-        <v>2.1978573339993002</v>
-      </c>
-      <c r="AE33">
-        <v>33</v>
-      </c>
-      <c r="AF33">
-        <v>0</v>
-      </c>
-      <c r="AG33">
-        <v>0</v>
-      </c>
-      <c r="AH33">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>43</v>
-      </c>
       <c r="B34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34">
         <v>40</v>
       </c>
       <c r="D34">
-        <v>640.21524930000305</v>
+        <v>3774.74291229248</v>
       </c>
       <c r="E34" t="s">
-        <v>177</v>
+        <v>138</v>
       </c>
       <c r="F34">
         <v>33</v>
       </c>
       <c r="G34">
-        <v>320.01122188568098</v>
+        <v>100.92551684379499</v>
       </c>
       <c r="H34" t="s">
-        <v>177</v>
+        <v>138</v>
       </c>
       <c r="I34">
         <v>33</v>
       </c>
       <c r="J34">
-        <v>466.90860319137499</v>
+        <v>302.64456987380902</v>
       </c>
       <c r="K34" t="s">
-        <v>177</v>
+        <v>139</v>
       </c>
       <c r="L34">
         <v>33</v>
       </c>
       <c r="M34">
-        <v>86400.131663084001</v>
+        <v>86400.140103101701</v>
       </c>
       <c r="P34">
-        <v>5.6045055389404297E-3</v>
+        <v>5.6214332580566398E-3</v>
       </c>
       <c r="Q34" t="s">
-        <v>178</v>
+        <v>140</v>
       </c>
       <c r="R34">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S34" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="T34">
-        <v>0.14530545799971101</v>
+        <v>8.1198459000006495E-2</v>
       </c>
       <c r="U34">
         <v>32</v>
@@ -5427,13 +5420,13 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X34" t="s">
-        <v>179</v>
+        <v>226</v>
       </c>
       <c r="Y34">
-        <v>0.75533995800014897</v>
+        <v>0.54410941700007198</v>
       </c>
       <c r="Z34">
         <v>32</v>
@@ -5442,13 +5435,13 @@
         <v>-1</v>
       </c>
       <c r="AB34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AD34">
-        <v>1.99812491700049</v>
+        <v>3.3834880430003902</v>
       </c>
       <c r="AE34">
         <v>33</v>
@@ -5460,96 +5453,96 @@
         <v>0</v>
       </c>
       <c r="AH34">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="B35">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C35">
         <v>40</v>
       </c>
       <c r="D35">
-        <v>86400.324173450397</v>
+        <v>1964.59009075164</v>
+      </c>
+      <c r="E35" t="s">
+        <v>142</v>
+      </c>
+      <c r="F35">
+        <v>34</v>
       </c>
       <c r="G35">
-        <v>76.000017881393404</v>
+        <v>136.314377784729</v>
       </c>
       <c r="H35" t="s">
-        <v>70</v>
+        <v>143</v>
       </c>
       <c r="I35">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="J35">
-        <v>132.477592945098</v>
+        <v>394.49784350395203</v>
       </c>
       <c r="K35" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="L35">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="M35">
-        <v>47.098084926605203</v>
-      </c>
-      <c r="N35" t="s">
-        <v>72</v>
-      </c>
-      <c r="O35">
-        <v>39</v>
+        <v>86400.115904331207</v>
       </c>
       <c r="P35">
-        <v>6.5302848815917899E-3</v>
+        <v>5.6524276733398403E-3</v>
       </c>
       <c r="Q35" t="s">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="R35">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="S35" t="s">
-        <v>74</v>
+        <v>145</v>
       </c>
       <c r="T35">
-        <v>0.147897666999597</v>
+        <v>8.3501915999931897E-2</v>
       </c>
       <c r="U35">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="V35">
         <v>0</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" t="s">
-        <v>74</v>
+        <v>145</v>
       </c>
       <c r="Y35">
-        <v>0.63420491699980597</v>
+        <v>0.84210574999997301</v>
       </c>
       <c r="Z35">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="AA35">
         <v>0</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC35" t="s">
-        <v>74</v>
+        <v>145</v>
       </c>
       <c r="AD35">
-        <v>3.9922276269999202</v>
+        <v>1.81597325100028</v>
       </c>
       <c r="AE35">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="AF35">
         <v>0</v>
@@ -5558,110 +5551,110 @@
         <v>0</v>
       </c>
       <c r="AH35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C36">
         <v>40</v>
       </c>
       <c r="D36">
-        <v>1297.5956439971901</v>
+        <v>98.0358052253723</v>
       </c>
       <c r="E36" t="s">
-        <v>32</v>
+        <v>146</v>
       </c>
       <c r="F36">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G36">
-        <v>77.707883358001695</v>
+        <v>1499.5055146217301</v>
       </c>
       <c r="H36" t="s">
-        <v>33</v>
+        <v>147</v>
       </c>
       <c r="I36">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="J36">
-        <v>256.97025418281498</v>
+        <v>453.13620591163601</v>
       </c>
       <c r="K36" t="s">
-        <v>33</v>
+        <v>147</v>
       </c>
       <c r="L36">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="M36">
-        <v>86400.128589868502</v>
+        <v>86400.137974739002</v>
       </c>
       <c r="P36">
-        <v>5.3551197052001901E-3</v>
+        <v>5.1372051239013602E-3</v>
       </c>
       <c r="Q36" t="s">
-        <v>34</v>
+        <v>148</v>
       </c>
       <c r="R36">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="S36" t="s">
-        <v>35</v>
+        <v>149</v>
       </c>
       <c r="T36">
-        <v>0.157853499999873</v>
+        <v>0.117617542000061</v>
       </c>
       <c r="U36">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="W36">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X36" t="s">
-        <v>35</v>
+        <v>227</v>
       </c>
       <c r="Y36">
-        <v>0.87887870899976395</v>
+        <v>0.38466891700045303</v>
       </c>
       <c r="Z36">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AB36">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC36" t="s">
-        <v>35</v>
+        <v>249</v>
       </c>
       <c r="AD36">
-        <v>2.4873180009999398</v>
+        <v>0.81504812500043</v>
       </c>
       <c r="AE36">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AH36">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:34" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B37">
         <v>6</v>
@@ -5670,49 +5663,49 @@
         <v>40</v>
       </c>
       <c r="D37">
-        <v>31.145901679992601</v>
+        <v>340.20367479324301</v>
       </c>
       <c r="E37" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F37">
         <v>31</v>
       </c>
       <c r="G37">
-        <v>320.65396547317499</v>
+        <v>59.518777132034302</v>
       </c>
       <c r="H37" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="I37">
         <v>31</v>
       </c>
       <c r="J37">
-        <v>293.428564310073</v>
+        <v>248.66281890869101</v>
       </c>
       <c r="K37" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="L37">
         <v>31</v>
       </c>
       <c r="M37">
-        <v>86400.134007453904</v>
+        <v>86400.133429527195</v>
       </c>
       <c r="P37">
-        <v>6.2503814697265599E-3</v>
+        <v>4.7066211700439401E-3</v>
       </c>
       <c r="Q37" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="R37">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="S37" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="T37">
-        <v>0.15854416599995599</v>
+        <v>9.1725875000065502E-2</v>
       </c>
       <c r="U37">
         <v>31</v>
@@ -5721,13 +5714,13 @@
         <v>0</v>
       </c>
       <c r="W37">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X37" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="Y37">
-        <v>0.76464012599990305</v>
+        <v>0.126252750000276</v>
       </c>
       <c r="Z37">
         <v>31</v>
@@ -5736,13 +5729,13 @@
         <v>0</v>
       </c>
       <c r="AB37">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="AD37">
-        <v>1.67764466700009</v>
+        <v>0.91174570899966001</v>
       </c>
       <c r="AE37">
         <v>31</v>
@@ -5754,194 +5747,194 @@
         <v>0</v>
       </c>
       <c r="AH37">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B38">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C38">
         <v>40</v>
       </c>
       <c r="D38">
-        <v>58.451675891876199</v>
+        <v>31.145901679992601</v>
       </c>
       <c r="E38" t="s">
-        <v>54</v>
+        <v>153</v>
       </c>
       <c r="F38">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G38">
-        <v>22.211640119552602</v>
+        <v>320.65396547317499</v>
       </c>
       <c r="H38" t="s">
-        <v>55</v>
+        <v>154</v>
       </c>
       <c r="I38">
-        <v>31.999999999999901</v>
+        <v>31</v>
       </c>
       <c r="J38">
-        <v>173.92218637466399</v>
+        <v>293.428564310073</v>
       </c>
       <c r="K38" t="s">
-        <v>56</v>
+        <v>154</v>
       </c>
       <c r="L38">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M38">
-        <v>86400.126599073395</v>
+        <v>86400.134007453904</v>
       </c>
       <c r="P38">
-        <v>4.5175552368164002E-3</v>
+        <v>6.2503814697265599E-3</v>
       </c>
       <c r="Q38" t="s">
-        <v>57</v>
+        <v>155</v>
       </c>
       <c r="R38">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="S38" t="s">
-        <v>58</v>
+        <v>156</v>
       </c>
       <c r="T38">
-        <v>0.16163216699987901</v>
+        <v>0.15854416599995599</v>
       </c>
       <c r="U38">
         <v>31</v>
       </c>
       <c r="V38">
-        <v>-0.999999999999996</v>
+        <v>0</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X38" t="s">
-        <v>217</v>
+        <v>156</v>
       </c>
       <c r="Y38">
-        <v>0.70187862500006304</v>
+        <v>0.76464012599990305</v>
       </c>
       <c r="Z38">
-        <v>32</v>
-      </c>
-      <c r="AA38" s="1">
-        <v>3.5527136788005001E-15</v>
+        <v>31</v>
+      </c>
+      <c r="AA38">
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AC38" t="s">
-        <v>217</v>
+        <v>156</v>
       </c>
       <c r="AD38">
-        <v>1.63539791699986</v>
+        <v>1.67764466700009</v>
       </c>
       <c r="AE38">
-        <v>32</v>
-      </c>
-      <c r="AF38" s="1">
-        <v>3.5527136788005001E-15</v>
+        <v>31</v>
+      </c>
+      <c r="AF38">
+        <v>0</v>
       </c>
       <c r="AG38">
         <v>0</v>
       </c>
       <c r="AH38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C39">
         <v>40</v>
       </c>
       <c r="D39">
-        <v>2330.9193391799899</v>
+        <v>4.9631543159484801</v>
       </c>
       <c r="E39" t="s">
-        <v>109</v>
+        <v>157</v>
       </c>
       <c r="F39">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="G39">
-        <v>58.3836863040924</v>
+        <v>6913.6652741432099</v>
       </c>
       <c r="H39" t="s">
-        <v>110</v>
+        <v>158</v>
       </c>
       <c r="I39">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="J39">
-        <v>181.586270332336</v>
+        <v>546.080072641372</v>
       </c>
       <c r="K39" t="s">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="L39">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="M39">
-        <v>86400.129125595093</v>
+        <v>86400.127148866595</v>
       </c>
       <c r="P39">
-        <v>6.0391426086425703E-3</v>
+        <v>5.1782131195068299E-3</v>
       </c>
       <c r="Q39" t="s">
-        <v>111</v>
+        <v>160</v>
       </c>
       <c r="R39">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="S39" t="s">
-        <v>112</v>
+        <v>161</v>
       </c>
       <c r="T39">
-        <v>0.162366374999692</v>
+        <v>0.11649966699997</v>
       </c>
       <c r="U39">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W39">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="X39" t="s">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c r="Y39">
-        <v>1.19237250100013</v>
+        <v>0.49047770899960502</v>
       </c>
       <c r="Z39">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="AA39">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AC39" t="s">
-        <v>244</v>
+        <v>161</v>
       </c>
       <c r="AD39">
-        <v>5.5275429610001003</v>
+        <v>1.0256034170006301</v>
       </c>
       <c r="AE39">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AF39">
         <v>0</v>
@@ -5950,96 +5943,96 @@
         <v>0</v>
       </c>
       <c r="AH39">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="B40">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C40">
         <v>40</v>
       </c>
       <c r="D40">
-        <v>362.63930082321099</v>
+        <v>79.188139438629094</v>
       </c>
       <c r="E40" t="s">
-        <v>36</v>
+        <v>162</v>
       </c>
       <c r="F40">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G40">
-        <v>78.8139390945434</v>
+        <v>610.82811737060501</v>
       </c>
       <c r="H40" t="s">
-        <v>36</v>
+        <v>163</v>
       </c>
       <c r="I40">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J40">
-        <v>297.10240054130497</v>
+        <v>276.89593887329102</v>
       </c>
       <c r="K40" t="s">
-        <v>36</v>
+        <v>163</v>
       </c>
       <c r="L40">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="M40">
-        <v>86400.132736921296</v>
+        <v>86400.126035213398</v>
       </c>
       <c r="P40">
-        <v>4.8964023590087804E-3</v>
+        <v>6.1039924621581997E-3</v>
       </c>
       <c r="Q40" t="s">
-        <v>37</v>
+        <v>163</v>
       </c>
       <c r="R40">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="S40" t="s">
-        <v>38</v>
+        <v>164</v>
       </c>
       <c r="T40">
-        <v>0.16448504199979599</v>
+        <v>0.105333333000089</v>
       </c>
       <c r="U40">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="V40">
         <v>0</v>
       </c>
       <c r="W40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X40" t="s">
-        <v>38</v>
+        <v>164</v>
       </c>
       <c r="Y40">
-        <v>0.51000645900057795</v>
+        <v>0.50584537499980797</v>
       </c>
       <c r="Z40">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="AA40">
         <v>0</v>
       </c>
       <c r="AB40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="s">
-        <v>240</v>
+        <v>164</v>
       </c>
       <c r="AD40">
-        <v>1.67395616799967</v>
+        <v>1.0728722090006999</v>
       </c>
       <c r="AE40">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="AF40">
         <v>0</v>
@@ -6048,96 +6041,96 @@
         <v>0</v>
       </c>
       <c r="AH40">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:34" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C41">
         <v>40</v>
       </c>
       <c r="D41">
-        <v>805.73928236961297</v>
+        <v>922.62835550308205</v>
       </c>
       <c r="E41" t="s">
-        <v>126</v>
+        <v>165</v>
       </c>
       <c r="F41">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G41">
-        <v>58.891531467437702</v>
+        <v>280.592938423156</v>
       </c>
       <c r="H41" t="s">
-        <v>126</v>
+        <v>165</v>
       </c>
       <c r="I41">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J41">
-        <v>259.028136491775</v>
+        <v>412.89148020744301</v>
       </c>
       <c r="K41" t="s">
-        <v>126</v>
+        <v>165</v>
       </c>
       <c r="L41">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M41">
-        <v>86400.1880934238</v>
+        <v>86400.128802537904</v>
       </c>
       <c r="P41">
-        <v>4.7945976257324201E-3</v>
+        <v>5.1181316375732396E-3</v>
       </c>
       <c r="Q41" t="s">
-        <v>126</v>
+        <v>166</v>
       </c>
       <c r="R41">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="S41" t="s">
-        <v>127</v>
+        <v>167</v>
       </c>
       <c r="T41">
-        <v>0.169992041000114</v>
+        <v>0.10184775000016</v>
       </c>
       <c r="U41">
         <v>32</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X41" t="s">
-        <v>127</v>
+        <v>167</v>
       </c>
       <c r="Y41">
-        <v>0.700133125999855</v>
+        <v>0.69615558399982502</v>
       </c>
       <c r="Z41">
         <v>32</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC41" t="s">
-        <v>127</v>
+        <v>250</v>
       </c>
       <c r="AD41">
-        <v>1.6987882510002199</v>
+        <v>3.37205650099986</v>
       </c>
       <c r="AE41">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AF41">
         <v>0</v>
@@ -6146,96 +6139,96 @@
         <v>0</v>
       </c>
       <c r="AH41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C42">
         <v>40</v>
       </c>
       <c r="D42">
-        <v>471.46557950973499</v>
+        <v>712.73984003067005</v>
       </c>
       <c r="E42" t="s">
-        <v>39</v>
+        <v>168</v>
       </c>
       <c r="F42">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G42">
-        <v>77.797639846801701</v>
+        <v>1518.63394331932</v>
       </c>
       <c r="H42" t="s">
-        <v>40</v>
+        <v>169</v>
       </c>
       <c r="I42">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="J42">
-        <v>244.49754166603</v>
+        <v>707.79996132850601</v>
       </c>
       <c r="K42" t="s">
-        <v>39</v>
+        <v>170</v>
       </c>
       <c r="L42">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M42">
-        <v>86400.1265144348</v>
+        <v>86400.211915969805</v>
       </c>
       <c r="P42">
-        <v>4.8739910125732396E-3</v>
+        <v>5.31005859375E-3</v>
       </c>
       <c r="Q42" t="s">
-        <v>41</v>
+        <v>171</v>
       </c>
       <c r="R42">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S42" t="s">
-        <v>42</v>
+        <v>172</v>
       </c>
       <c r="T42">
-        <v>0.184896415999901</v>
+        <v>0.134515959000054</v>
       </c>
       <c r="U42">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="V42">
         <v>-1</v>
       </c>
       <c r="W42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X42" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="Y42">
-        <v>0.99781641700064905</v>
+        <v>0.85145383400049401</v>
       </c>
       <c r="Z42">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AA42">
         <v>-1</v>
       </c>
       <c r="AB42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC42" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="AD42">
-        <v>3.3030031670004898</v>
+        <v>2.5544875010000299</v>
       </c>
       <c r="AE42">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AF42">
         <v>-1</v>
@@ -6244,292 +6237,292 @@
         <v>-1</v>
       </c>
       <c r="AH42">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C43">
         <v>40</v>
       </c>
       <c r="D43">
-        <v>396.46075916290198</v>
+        <v>5505.72230434417</v>
       </c>
       <c r="E43" t="s">
-        <v>23</v>
+        <v>173</v>
       </c>
       <c r="F43">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G43">
-        <v>51.4951264858245</v>
+        <v>580.17795109748795</v>
       </c>
       <c r="H43" t="s">
-        <v>24</v>
+        <v>173</v>
       </c>
       <c r="I43">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J43">
-        <v>215.09952902793799</v>
+        <v>479.90765690803499</v>
       </c>
       <c r="K43" t="s">
-        <v>24</v>
+        <v>174</v>
       </c>
       <c r="L43">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M43">
-        <v>86400.1290633678</v>
+        <v>86400.134572505907</v>
       </c>
       <c r="P43">
-        <v>5.5739879608154297E-3</v>
+        <v>5.4419040679931597E-3</v>
       </c>
       <c r="Q43" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="R43">
+        <v>32</v>
+      </c>
+      <c r="S43" t="s">
+        <v>176</v>
+      </c>
+      <c r="T43">
+        <v>0.103053875000114</v>
+      </c>
+      <c r="U43">
+        <v>34</v>
+      </c>
+      <c r="V43">
+        <v>-1</v>
+      </c>
+      <c r="W43">
+        <v>2</v>
+      </c>
+      <c r="X43" t="s">
+        <v>229</v>
+      </c>
+      <c r="Y43">
+        <v>0.50271679199977304</v>
+      </c>
+      <c r="Z43">
         <v>33</v>
       </c>
-      <c r="S43" t="s">
-        <v>26</v>
-      </c>
-      <c r="T43">
-        <v>0.19206783400022601</v>
-      </c>
-      <c r="U43">
-        <v>26</v>
-      </c>
-      <c r="V43">
-        <v>-10</v>
-      </c>
-      <c r="W43">
-        <v>-7</v>
-      </c>
-      <c r="X43" t="s">
-        <v>213</v>
-      </c>
-      <c r="Y43">
-        <v>0.43922858400037501</v>
-      </c>
-      <c r="Z43">
-        <v>36</v>
-      </c>
       <c r="AA43">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AB43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC43" t="s">
-        <v>239</v>
+        <v>176</v>
       </c>
       <c r="AD43">
-        <v>1.8165461259995901</v>
+        <v>3.8542224180000599</v>
       </c>
       <c r="AE43">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AH43">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="B44">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C44">
         <v>40</v>
       </c>
       <c r="D44">
-        <v>6526.2341415882102</v>
+        <v>640.21524930000305</v>
       </c>
       <c r="E44" t="s">
-        <v>79</v>
+        <v>177</v>
       </c>
       <c r="F44">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G44">
-        <v>64.794146537780705</v>
+        <v>320.01122188568098</v>
       </c>
       <c r="H44" t="s">
-        <v>80</v>
+        <v>177</v>
       </c>
       <c r="I44">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J44">
-        <v>234.16041851043701</v>
+        <v>466.90860319137499</v>
       </c>
       <c r="K44" t="s">
-        <v>79</v>
+        <v>177</v>
       </c>
       <c r="L44">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M44">
-        <v>86400.141325473698</v>
+        <v>86400.131663084001</v>
       </c>
       <c r="P44">
-        <v>4.3635368347167899E-3</v>
+        <v>5.6045055389404297E-3</v>
       </c>
       <c r="Q44" t="s">
-        <v>81</v>
+        <v>178</v>
       </c>
       <c r="R44">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="S44" t="s">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="T44">
-        <v>0.195492166999883</v>
+        <v>0.14530545799971101</v>
       </c>
       <c r="U44">
-        <v>35</v>
-      </c>
-      <c r="V44" s="1">
-        <v>-7.1054273576010003E-15</v>
+        <v>32</v>
+      </c>
+      <c r="V44">
+        <v>-1</v>
       </c>
       <c r="W44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X44" t="s">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="Y44">
-        <v>1.3690103760000001</v>
+        <v>0.75533995800014897</v>
       </c>
       <c r="Z44">
-        <v>35</v>
-      </c>
-      <c r="AA44" s="1">
-        <v>-7.1054273576010003E-15</v>
+        <v>32</v>
+      </c>
+      <c r="AA44">
+        <v>-1</v>
       </c>
       <c r="AB44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC44" t="s">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="AD44">
-        <v>5.68862400299985</v>
+        <v>1.99812491700049</v>
       </c>
       <c r="AE44">
-        <v>35</v>
-      </c>
-      <c r="AF44" s="1">
-        <v>-7.1054273576010003E-15</v>
+        <v>33</v>
+      </c>
+      <c r="AF44">
+        <v>0</v>
       </c>
       <c r="AG44">
         <v>0</v>
       </c>
       <c r="AH44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="B45">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C45">
         <v>40</v>
       </c>
       <c r="D45">
-        <v>847.00700283050503</v>
+        <v>271.16198706626801</v>
       </c>
       <c r="E45" t="s">
-        <v>64</v>
+        <v>180</v>
       </c>
       <c r="F45">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G45">
-        <v>58.091557264328003</v>
+        <v>94.3208456039428</v>
       </c>
       <c r="H45" t="s">
-        <v>64</v>
+        <v>180</v>
       </c>
       <c r="I45">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="J45">
-        <v>197.25004124641401</v>
+        <v>332.61604619026099</v>
       </c>
       <c r="K45" t="s">
-        <v>64</v>
+        <v>180</v>
       </c>
       <c r="L45">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="M45">
-        <v>86400.126175403595</v>
+        <v>86400.134548902497</v>
       </c>
       <c r="P45">
-        <v>5.2807331085205E-3</v>
+        <v>4.8720836639404297E-3</v>
       </c>
       <c r="Q45" t="s">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="R45">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="S45" t="s">
-        <v>66</v>
+        <v>181</v>
       </c>
       <c r="T45">
-        <v>0.22201533399993401</v>
+        <v>0.104308082999978</v>
       </c>
       <c r="U45">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V45">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="W45">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="X45" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="Y45">
-        <v>1.1471546250004301</v>
+        <v>0.544640124999205</v>
       </c>
       <c r="Z45">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AA45">
         <v>0</v>
       </c>
       <c r="AB45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="AD45">
-        <v>3.39485687699925</v>
+        <v>2.4789781680001299</v>
       </c>
       <c r="AE45">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AF45">
         <v>0</v>
@@ -6538,96 +6531,96 @@
         <v>0</v>
       </c>
       <c r="AH45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C46">
         <v>40</v>
       </c>
       <c r="D46">
-        <v>2946.5776097774501</v>
+        <v>291.48174500465302</v>
       </c>
       <c r="E46" t="s">
+        <v>182</v>
+      </c>
+      <c r="F46">
         <v>29</v>
       </c>
-      <c r="F46">
-        <v>36</v>
-      </c>
       <c r="G46">
-        <v>45.887658596038797</v>
+        <v>213.53333497047399</v>
       </c>
       <c r="H46" t="s">
-        <v>30</v>
+        <v>183</v>
       </c>
       <c r="I46">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J46">
-        <v>111.08167362213101</v>
+        <v>478.408534049987</v>
       </c>
       <c r="K46" t="s">
-        <v>30</v>
+        <v>184</v>
       </c>
       <c r="L46">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="M46">
-        <v>86400.133324861497</v>
+        <v>86400.129339218096</v>
       </c>
       <c r="P46">
-        <v>4.7135353088378898E-3</v>
+        <v>5.0356388092040998E-3</v>
       </c>
       <c r="Q46" t="s">
-        <v>30</v>
+        <v>185</v>
       </c>
       <c r="R46">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S46" t="s">
-        <v>31</v>
+        <v>186</v>
       </c>
       <c r="T46">
-        <v>0.22504466700001999</v>
+        <v>0.14090329200007501</v>
       </c>
       <c r="U46">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="V46">
         <v>0</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X46" t="s">
-        <v>31</v>
+        <v>186</v>
       </c>
       <c r="Y46">
-        <v>1.8452987929995199</v>
+        <v>0.50693925000086804</v>
       </c>
       <c r="Z46">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AA46">
         <v>0</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AC46" t="s">
-        <v>31</v>
+        <v>252</v>
       </c>
       <c r="AD46">
-        <v>5.5470325030000804</v>
+        <v>1.01202449999982</v>
       </c>
       <c r="AE46">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AF46">
         <v>0</v>
@@ -6636,96 +6629,96 @@
         <v>0</v>
       </c>
       <c r="AH46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="B47">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C47">
         <v>40</v>
       </c>
       <c r="D47">
-        <v>1909.8805825710201</v>
+        <v>50.2884037494659</v>
       </c>
       <c r="E47" t="s">
-        <v>128</v>
+        <v>187</v>
       </c>
       <c r="F47">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G47">
-        <v>52.664197683334301</v>
+        <v>89.7342205047607</v>
       </c>
       <c r="H47" t="s">
-        <v>129</v>
+        <v>188</v>
       </c>
       <c r="I47">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J47">
-        <v>176.476865291595</v>
+        <v>544.07556653022698</v>
       </c>
       <c r="K47" t="s">
-        <v>130</v>
+        <v>187</v>
       </c>
       <c r="L47">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M47">
-        <v>86400.145117759705</v>
+        <v>86400.1261193752</v>
       </c>
       <c r="P47">
-        <v>6.1647891998290998E-3</v>
+        <v>5.8310031890869097E-3</v>
       </c>
       <c r="Q47" t="s">
-        <v>131</v>
+        <v>189</v>
       </c>
       <c r="R47">
+        <v>33</v>
+      </c>
+      <c r="S47" t="s">
+        <v>190</v>
+      </c>
+      <c r="T47">
+        <v>0.13723908300016699</v>
+      </c>
+      <c r="U47">
+        <v>33</v>
+      </c>
+      <c r="V47">
+        <v>-2</v>
+      </c>
+      <c r="W47">
+        <v>0</v>
+      </c>
+      <c r="X47" t="s">
+        <v>230</v>
+      </c>
+      <c r="Y47">
+        <v>1.22124062599959</v>
+      </c>
+      <c r="Z47">
         <v>35</v>
       </c>
-      <c r="S47" t="s">
-        <v>132</v>
-      </c>
-      <c r="T47">
-        <v>0.23984020799980499</v>
-      </c>
-      <c r="U47">
-        <v>38</v>
-      </c>
-      <c r="V47">
-        <v>0</v>
-      </c>
-      <c r="W47">
-        <v>3</v>
-      </c>
-      <c r="X47" t="s">
-        <v>132</v>
-      </c>
-      <c r="Y47">
-        <v>1.54557029199986</v>
-      </c>
-      <c r="Z47">
-        <v>38</v>
-      </c>
       <c r="AA47">
         <v>0</v>
       </c>
       <c r="AB47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC47" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="AD47">
-        <v>10.299458254000401</v>
+        <v>5.3473507110002103</v>
       </c>
       <c r="AE47">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="AF47">
         <v>0</v>
@@ -6734,81 +6727,81 @@
         <v>0</v>
       </c>
       <c r="AH47">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:34" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="B48">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C48">
         <v>40</v>
       </c>
       <c r="D48">
-        <v>78285.793434858293</v>
+        <v>28681.8346641063</v>
       </c>
       <c r="E48" t="s">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="F48">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G48">
-        <v>77.328538656234699</v>
+        <v>638.05624175071705</v>
       </c>
       <c r="H48" t="s">
-        <v>76</v>
+        <v>192</v>
       </c>
       <c r="I48">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="J48">
-        <v>224.450894832611</v>
+        <v>463.24853658676102</v>
       </c>
       <c r="K48" t="s">
-        <v>76</v>
+        <v>193</v>
       </c>
       <c r="L48">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="M48">
-        <v>86400.140725135803</v>
+        <v>86400.312841892199</v>
       </c>
       <c r="P48">
-        <v>5.2385330200195304E-3</v>
+        <v>5.4316520690917899E-3</v>
       </c>
       <c r="Q48" t="s">
-        <v>77</v>
+        <v>194</v>
       </c>
       <c r="R48">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="S48" t="s">
-        <v>78</v>
+        <v>195</v>
       </c>
       <c r="T48">
-        <v>0.32934462499997602</v>
+        <v>7.6273958000001502E-2</v>
       </c>
       <c r="U48">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="V48">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="W48">
-        <v>-10</v>
+        <v>1</v>
       </c>
       <c r="X48" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="Y48">
-        <v>1.09348520799994</v>
+        <v>0.83446166699923197</v>
       </c>
       <c r="Z48">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="AA48">
         <v>0</v>
@@ -6817,13 +6810,13 @@
         <v>1</v>
       </c>
       <c r="AC48" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="AD48">
-        <v>3.1117815429997702</v>
+        <v>3.0783139179993602</v>
       </c>
       <c r="AE48">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="AF48">
         <v>0</v>
@@ -6835,87 +6828,93 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="B49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C49">
         <v>40</v>
       </c>
       <c r="D49">
-        <v>86400.874973535494</v>
+        <v>24.768089056015</v>
+      </c>
+      <c r="E49" t="s">
+        <v>196</v>
+      </c>
+      <c r="F49">
+        <v>23</v>
       </c>
       <c r="G49">
-        <v>70.089067459106403</v>
+        <v>17601.845165967901</v>
       </c>
       <c r="H49" t="s">
-        <v>50</v>
+        <v>197</v>
       </c>
       <c r="I49">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J49">
-        <v>230.956568717956</v>
+        <v>1496.15870833396</v>
       </c>
       <c r="K49" t="s">
-        <v>51</v>
+        <v>198</v>
       </c>
       <c r="L49">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="M49">
-        <v>86400.140295505495</v>
+        <v>86400.219609498905</v>
       </c>
       <c r="P49">
-        <v>5.2533149719238203E-3</v>
+        <v>4.7314167022705E-3</v>
       </c>
       <c r="Q49" t="s">
-        <v>52</v>
+        <v>199</v>
       </c>
       <c r="R49">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="S49" t="s">
-        <v>53</v>
+        <v>200</v>
       </c>
       <c r="T49">
-        <v>0.360892499999863</v>
+        <v>0.13343433399995699</v>
       </c>
       <c r="U49">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="V49">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="W49">
-        <v>-8</v>
+        <v>4</v>
       </c>
       <c r="X49" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="Y49">
-        <v>1.00651333400037</v>
+        <v>0.47714245899987801</v>
       </c>
       <c r="Z49">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="AA49">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AB49">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC49" t="s">
-        <v>241</v>
+        <v>200</v>
       </c>
       <c r="AD49">
-        <v>3.8565233350000199</v>
+        <v>1.4057622509999399</v>
       </c>
       <c r="AE49">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="AF49">
         <v>0</v>
@@ -6924,96 +6923,96 @@
         <v>0</v>
       </c>
       <c r="AH49">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:34" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="B50">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C50">
         <v>40</v>
       </c>
       <c r="D50">
-        <v>907.86760544776905</v>
+        <v>20.868867158889699</v>
       </c>
       <c r="E50" t="s">
-        <v>133</v>
+        <v>201</v>
       </c>
       <c r="F50">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G50">
-        <v>79.067918539047199</v>
+        <v>5634.1728641986801</v>
       </c>
       <c r="H50" t="s">
-        <v>134</v>
+        <v>202</v>
       </c>
       <c r="I50">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="J50">
-        <v>293.41959142684902</v>
+        <v>1068.1284990310601</v>
       </c>
       <c r="K50" t="s">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="L50">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="M50">
-        <v>86400.082375526399</v>
+        <v>86400.086030006394</v>
       </c>
       <c r="P50">
-        <v>6.0026645660400304E-3</v>
+        <v>4.53543663024902E-3</v>
       </c>
       <c r="Q50" t="s">
-        <v>136</v>
+        <v>203</v>
       </c>
       <c r="R50">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="S50" t="s">
-        <v>137</v>
+        <v>204</v>
       </c>
       <c r="T50">
-        <v>0.39023537499997402</v>
+        <v>0.104485040999861</v>
       </c>
       <c r="U50">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="V50">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="W50">
-        <v>-15</v>
+        <v>6</v>
       </c>
       <c r="X50" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="Y50">
-        <v>0.82609883400073103</v>
+        <v>0.34610658299970898</v>
       </c>
       <c r="Z50">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AA50">
         <v>0</v>
       </c>
       <c r="AB50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AC50" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
       <c r="AD50">
-        <v>2.0154344180000399</v>
+        <v>1.33293304200014</v>
       </c>
       <c r="AE50">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AF50">
         <v>0</v>
@@ -7022,96 +7021,96 @@
         <v>0</v>
       </c>
       <c r="AH50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:34" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="B51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C51">
         <v>40</v>
       </c>
       <c r="D51">
-        <v>729.35242557525601</v>
+        <v>18.745156764984099</v>
       </c>
       <c r="E51" t="s">
-        <v>97</v>
+        <v>205</v>
       </c>
       <c r="F51">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G51">
-        <v>58.242346525192197</v>
+        <v>163.14162302017201</v>
       </c>
       <c r="H51" t="s">
-        <v>98</v>
+        <v>205</v>
       </c>
       <c r="I51">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="J51">
-        <v>291.66989302635102</v>
+        <v>452.50598287582397</v>
       </c>
       <c r="K51" t="s">
-        <v>99</v>
+        <v>205</v>
       </c>
       <c r="L51">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M51">
-        <v>86400.160304784702</v>
+        <v>86400.124464988694</v>
       </c>
       <c r="P51">
-        <v>5.1820278167724601E-3</v>
+        <v>4.9333572387695304E-3</v>
       </c>
       <c r="Q51" t="s">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="R51">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="S51" t="s">
-        <v>101</v>
+        <v>207</v>
       </c>
       <c r="T51">
-        <v>0.39884087499967702</v>
+        <v>9.0025083000000394E-2</v>
       </c>
       <c r="U51">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="V51">
         <v>0</v>
       </c>
       <c r="W51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X51" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="Y51">
-        <v>1.5459725010005001</v>
+        <v>0.32029962500018799</v>
       </c>
       <c r="Z51">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="AA51">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AB51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC51" t="s">
-        <v>101</v>
+        <v>207</v>
       </c>
       <c r="AD51">
-        <v>9.5797322550006303</v>
+        <v>0.65302429199982703</v>
       </c>
       <c r="AE51">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="AF51">
         <v>0</v>
@@ -7120,7 +7119,7 @@
         <v>0</v>
       </c>
       <c r="AH51">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -7134,17 +7133,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7588DEFA-C30B-4927-B0B6-2BE344E4D0E0}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.140625" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" customWidth="1"/>
-    <col min="3" max="3" width="34.85546875" customWidth="1"/>
-    <col min="4" max="6" width="33.42578125" customWidth="1"/>
-    <col min="7" max="8" width="24.85546875" customWidth="1"/>
-    <col min="9" max="9" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" customWidth="1"/>
+    <col min="3" max="3" width="34.81640625" customWidth="1"/>
+    <col min="4" max="6" width="33.453125" customWidth="1"/>
+    <col min="7" max="8" width="24.81640625" customWidth="1"/>
+    <col min="9" max="9" width="17.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>270</v>
       </c>
@@ -7176,7 +7175,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>3</v>
       </c>
@@ -7217,7 +7216,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>4</v>
       </c>
@@ -7258,7 +7257,7 @@
         <v>34.4</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>5</v>
       </c>
@@ -7299,7 +7298,7 @@
         <v>32.700000000000003</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>6</v>
       </c>
@@ -7340,7 +7339,7 @@
         <v>28.7</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>7</v>
       </c>
@@ -7381,7 +7380,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>270</v>
       </c>
@@ -7410,7 +7409,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>3</v>
       </c>
@@ -7424,7 +7423,7 @@
       </c>
       <c r="D13">
         <f>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[duration_iqcp])</f>
-        <v>59.419794297218289</v>
+        <v>59.419794297218303</v>
       </c>
       <c r="E13">
         <f>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[duration_ilp])</f>
@@ -7442,12 +7441,12 @@
         <f>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[time_taken k=3])</f>
         <v>2.6703245053998161</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13">
         <f>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[duration_greedy])</f>
         <v>5.2127599716186492E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>4</v>
       </c>
@@ -7465,7 +7464,7 @@
       </c>
       <c r="E14">
         <f>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[duration_ilp])</f>
-        <v>252.69481949806172</v>
+        <v>252.69481949806169</v>
       </c>
       <c r="F14">
         <f>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[time_taken k=1])</f>
@@ -7479,12 +7478,12 @@
         <f>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[time_taken k=3])</f>
         <v>2.9654247012997943</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14">
         <f>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[duration_greedy])</f>
-        <v>5.060338973999017E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+        <v>5.0603389739990162E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>5</v>
       </c>
@@ -7498,11 +7497,11 @@
       </c>
       <c r="D15">
         <f>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[duration_iqcp])</f>
-        <v>84.239138317108086</v>
+        <v>84.239138317108072</v>
       </c>
       <c r="E15">
         <f>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[duration_ilp])</f>
-        <v>299.32945880889838</v>
+        <v>299.32945880889844</v>
       </c>
       <c r="F15">
         <f>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[time_taken k=1])</f>
@@ -7514,14 +7513,14 @@
       </c>
       <c r="H15">
         <f>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[time_taken k=3])</f>
-        <v>3.3941497476002001</v>
-      </c>
-      <c r="I15" s="6">
+        <v>3.3941497476002005</v>
+      </c>
+      <c r="I15">
         <f>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[duration_greedy])</f>
         <v>5.1291227340698204E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>6</v>
       </c>
@@ -7539,11 +7538,11 @@
       </c>
       <c r="E16">
         <f>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[duration_ilp])</f>
-        <v>339.81339509487111</v>
+        <v>339.81339509487117</v>
       </c>
       <c r="F16">
         <f>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[time_taken k=1])</f>
-        <v>0.14863442910000188</v>
+        <v>0.14863442910000191</v>
       </c>
       <c r="G16">
         <f>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[time_taken k=2])</f>
@@ -7551,14 +7550,14 @@
       </c>
       <c r="H16">
         <f>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[time_taken k=3])</f>
-        <v>2.6389324594002481</v>
-      </c>
-      <c r="I16" s="6">
+        <v>2.6389324594002486</v>
+      </c>
+      <c r="I16">
         <f>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[duration_greedy])</f>
-        <v>5.5935859680175748E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+        <v>5.593585968017574E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>7</v>
       </c>
@@ -7568,7 +7567,7 @@
       </c>
       <c r="C17">
         <f>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[duration_miqcp])</f>
-        <v>86400.161110544184</v>
+        <v>86400.16111054417</v>
       </c>
       <c r="D17">
         <f>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[duration_iqcp])</f>
@@ -7576,7 +7575,7 @@
       </c>
       <c r="E17">
         <f>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[duration_ilp])</f>
-        <v>648.97580950259953</v>
+        <v>648.97580950259965</v>
       </c>
       <c r="F17">
         <f>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[time_taken k=1])</f>
@@ -7584,13 +7583,13 @@
       </c>
       <c r="G17">
         <f>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[time_taken k=2])</f>
-        <v>0.63603409189990845</v>
+        <v>0.63603409189990856</v>
       </c>
       <c r="H17">
         <f>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[time_taken k=3])</f>
-        <v>2.3715221718000006</v>
-      </c>
-      <c r="I17" s="6">
+        <v>2.3715221718000001</v>
+      </c>
+      <c r="I17">
         <f>AVERAGEIF(Table1[root degree],Table3[[#This Row],[Grado raíz]],Table1[duration_greedy])</f>
         <v>5.1727056503295867E-3</v>
       </c>
@@ -7608,21 +7607,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1612F500-8D23-450B-9D9A-1CB19CC22A52}">
   <dimension ref="A1:J51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="13.5703125" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" customWidth="1"/>
-    <col min="8" max="9" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.85546875" customWidth="1"/>
-    <col min="11" max="11" width="19.7109375" customWidth="1"/>
-    <col min="12" max="12" width="23.5703125" customWidth="1"/>
+    <col min="1" max="2" width="13.54296875" customWidth="1"/>
+    <col min="3" max="3" width="13.1796875" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" customWidth="1"/>
+    <col min="5" max="5" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.453125" customWidth="1"/>
+    <col min="7" max="7" width="17.7265625" customWidth="1"/>
+    <col min="8" max="9" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.81640625" customWidth="1"/>
+    <col min="11" max="11" width="19.7265625" customWidth="1"/>
+    <col min="12" max="12" width="23.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7654,7 +7653,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -7683,7 +7682,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -7712,7 +7711,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -7741,7 +7740,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -7770,7 +7769,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -7799,7 +7798,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -7828,7 +7827,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -7857,7 +7856,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -7886,7 +7885,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -7915,7 +7914,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -7944,7 +7943,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -7973,7 +7972,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -7999,7 +7998,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -8028,7 +8027,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -8057,7 +8056,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -8086,7 +8085,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -8115,7 +8114,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -8144,7 +8143,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -8173,7 +8172,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -8202,7 +8201,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -8231,7 +8230,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -8260,7 +8259,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -8289,7 +8288,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -8318,7 +8317,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -8347,7 +8346,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -8379,7 +8378,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -8408,7 +8407,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -8437,7 +8436,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -8466,7 +8465,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -8495,7 +8494,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -8524,7 +8523,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -8553,7 +8552,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -8582,7 +8581,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -8611,7 +8610,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -8640,7 +8639,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -8669,7 +8668,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -8698,7 +8697,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -8727,7 +8726,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -8756,7 +8755,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -8785,7 +8784,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -8814,7 +8813,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -8843,7 +8842,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -8872,7 +8871,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -8901,7 +8900,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -8930,7 +8929,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -8959,7 +8958,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -8988,7 +8987,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -9017,7 +9016,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -9046,7 +9045,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -9075,7 +9074,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -9115,18 +9114,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE00FF7C-78DF-4F44-91A2-C4452CAEBB34}">
   <dimension ref="A1:J51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="13.5703125" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" customWidth="1"/>
+    <col min="1" max="2" width="13.54296875" customWidth="1"/>
+    <col min="3" max="3" width="13.81640625" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.140625" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" customWidth="1"/>
-    <col min="8" max="10" width="16.5703125" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" customWidth="1"/>
+    <col min="7" max="7" width="17.7265625" customWidth="1"/>
+    <col min="8" max="10" width="16.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9158,7 +9157,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -9190,7 +9189,7 @@
         <v>2.9789236259994101</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -9222,7 +9221,7 @@
         <v>3.1687015020006499</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -9254,7 +9253,7 @@
         <v>2.1978573339993002</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -9286,7 +9285,7 @@
         <v>1.8165461259995901</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -9318,7 +9317,7 @@
         <v>1.4178213759996601</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -9350,7 +9349,7 @@
         <v>5.5470325030000804</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -9382,7 +9381,7 @@
         <v>2.4873180009999398</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -9414,7 +9413,7 @@
         <v>1.67395616799967</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -9446,7 +9445,7 @@
         <v>3.3030031670004898</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -9478,7 +9477,7 @@
         <v>2.1120852509993702</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -9510,7 +9509,7 @@
         <v>1.8838435839998</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -9542,7 +9541,7 @@
         <v>3.8565233350000199</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -9574,7 +9573,7 @@
         <v>1.63539791699986</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -9606,7 +9605,7 @@
         <v>3.97558945999935</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -9638,7 +9637,7 @@
         <v>3.39485687699925</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -9670,7 +9669,7 @@
         <v>1.18862187499962</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -9702,7 +9701,7 @@
         <v>3.9922276269999202</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -9734,7 +9733,7 @@
         <v>3.1117815429997702</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -9766,7 +9765,7 @@
         <v>5.68862400299985</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -9798,7 +9797,7 @@
         <v>0.92678079200049901</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -9830,7 +9829,7 @@
         <v>0.97163041700059605</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -9862,7 +9861,7 @@
         <v>7.6424404210001704</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -9894,7 +9893,7 @@
         <v>9.5797322550006303</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -9926,7 +9925,7 @@
         <v>1.73933054200006</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -9958,7 +9957,7 @@
         <v>1.1891566680005701</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -9990,7 +9989,7 @@
         <v>5.5275429610001003</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -10022,7 +10021,7 @@
         <v>3.4563811259995401</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -10054,7 +10053,7 @@
         <v>1.1719093760002499</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -10086,7 +10085,7 @@
         <v>0.96458545899986303</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -10118,7 +10117,7 @@
         <v>1.6987882510002199</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -10150,7 +10149,7 @@
         <v>10.299458254000401</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -10182,7 +10181,7 @@
         <v>2.0154344180000399</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -10214,7 +10213,7 @@
         <v>3.3834880430003902</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -10246,7 +10245,7 @@
         <v>1.81597325100028</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -10278,7 +10277,7 @@
         <v>0.81504812500043</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -10310,7 +10309,7 @@
         <v>0.91174570899966001</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -10342,7 +10341,7 @@
         <v>1.67764466700009</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -10374,7 +10373,7 @@
         <v>1.0256034170006301</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -10406,7 +10405,7 @@
         <v>1.0728722090006999</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -10438,7 +10437,7 @@
         <v>3.37205650099986</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -10470,7 +10469,7 @@
         <v>2.5544875010000299</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -10502,7 +10501,7 @@
         <v>3.8542224180000599</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -10534,7 +10533,7 @@
         <v>1.99812491700049</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -10566,7 +10565,7 @@
         <v>2.4789781680001299</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -10598,7 +10597,7 @@
         <v>1.01202449999982</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -10630,7 +10629,7 @@
         <v>5.3473507110002103</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -10662,7 +10661,7 @@
         <v>3.0783139179993602</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -10694,7 +10693,7 @@
         <v>1.4057622509999399</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -10726,7 +10725,7 @@
         <v>1.33293304200014</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -10769,18 +10768,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C677375-EC2A-4103-B5E1-7B57AD320C83}">
   <dimension ref="A1:E51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" customWidth="1"/>
-    <col min="3" max="3" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="20.28515625" customWidth="1"/>
-    <col min="6" max="6" width="21.28515625" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" customWidth="1"/>
-    <col min="8" max="8" width="23.5703125" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" customWidth="1"/>
+    <col min="2" max="2" width="13.7265625" customWidth="1"/>
+    <col min="3" max="3" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="20.26953125" customWidth="1"/>
+    <col min="6" max="6" width="21.26953125" customWidth="1"/>
+    <col min="7" max="7" width="19.7265625" customWidth="1"/>
+    <col min="8" max="8" width="23.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10797,7 +10796,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -10814,7 +10813,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -10831,7 +10830,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -10848,7 +10847,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -10865,7 +10864,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -10882,7 +10881,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -10899,7 +10898,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -10916,7 +10915,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -10933,7 +10932,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -10950,7 +10949,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -10967,7 +10966,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -10984,7 +10983,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -11001,7 +11000,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -11018,7 +11017,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -11035,7 +11034,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -11052,7 +11051,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -11069,7 +11068,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -11086,7 +11085,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -11103,7 +11102,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -11120,7 +11119,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -11137,7 +11136,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -11154,7 +11153,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -11171,7 +11170,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -11188,7 +11187,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -11205,7 +11204,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -11222,7 +11221,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -11239,7 +11238,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -11256,7 +11255,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -11273,7 +11272,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -11290,7 +11289,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -11307,7 +11306,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -11324,7 +11323,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -11341,7 +11340,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -11358,7 +11357,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -11375,7 +11374,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -11392,7 +11391,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -11409,7 +11408,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -11426,7 +11425,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -11443,7 +11442,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -11460,7 +11459,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -11477,7 +11476,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -11494,7 +11493,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -11511,7 +11510,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -11528,7 +11527,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -11545,7 +11544,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -11562,7 +11561,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -11579,7 +11578,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -11596,7 +11595,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -11613,7 +11612,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -11630,7 +11629,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -11658,21 +11657,21 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20B4FA2E-9AEB-4E79-9A8E-6278524DAB1E}">
   <dimension ref="A2:AH6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.26953125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="19" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -11743,7 +11742,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>32</v>
       </c>
@@ -11814,7 +11813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -11918,7 +11917,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>25</v>
       </c>
